--- a/wwwroot/ExcelModel/Primark_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Primark_PHY_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B3287F-BC59-4147-8B16-54281F146806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614AA0EA-3A26-4859-93DA-C58CA0B6019B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2508" yWindow="2508" windowWidth="17280" windowHeight="8880" firstSheet="19" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -42,11 +42,6 @@
     <sheet name="DryingRate" sheetId="41" r:id="rId27"/>
   </sheets>
   <definedNames>
-    <definedName name="OLE_LINK32" localSheetId="8">'PM06'!$A$54</definedName>
-    <definedName name="OLE_LINK36" localSheetId="7">PM03PM05!$A$32</definedName>
-    <definedName name="OLE_LINK36" localSheetId="8">'PM06'!#REF!</definedName>
-    <definedName name="OLE_LINK36" localSheetId="9">PM07PM08!#REF!</definedName>
-    <definedName name="OLE_LINK36" localSheetId="10">'PM23&amp;AR(TABER)'!#REF!</definedName>
     <definedName name="ReportNumber" localSheetId="12">Abrasion!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="3">Absorbency!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="2">Accelerotor!$M$1</definedName>
@@ -54,7 +49,7 @@
     <definedName name="ReportNumber" localSheetId="4">'ASTM F963-23'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="5">'Attachment Strength'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="18">'Bursting Strength'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="19">'Bursting Strength-G'!#REF!</definedName>
+    <definedName name="ReportNumber" localSheetId="19">'Bursting Strength-G'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="26">DryingRate!$J$1</definedName>
     <definedName name="ReportNumber" localSheetId="11">'Fibre Proof Properties'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="24">Hydrostatichead!$M$1</definedName>
@@ -65,7 +60,7 @@
     <definedName name="ReportNumber" localSheetId="9">PM07PM08!$J$1</definedName>
     <definedName name="ReportNumber" localSheetId="10">'PM23&amp;AR(TABER)'!$J$1</definedName>
     <definedName name="ReportNumber" localSheetId="20">'Seam Slippage&amp;Strength'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="21">'Seam Slippage&amp;Strength-G'!#REF!</definedName>
+    <definedName name="ReportNumber" localSheetId="21">'Seam Slippage&amp;Strength-G'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="14">'Stretch&amp;Recovery of Elastic'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="16">'Tearing Strength'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="17">'Tensile Strength'!$M$1</definedName>
@@ -4869,12 +4864,12 @@
       <c r="P3" s="61"/>
       <c r="Q3" s="24"/>
       <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
+      <c r="S3" s="148"/>
+      <c r="T3" s="148"/>
+      <c r="U3" s="148"/>
+      <c r="V3" s="148"/>
+      <c r="W3" s="148"/>
+      <c r="X3" s="148"/>
       <c r="Y3" s="24"/>
       <c r="Z3" s="24"/>
       <c r="AA3" s="24"/>
@@ -5420,7 +5415,7 @@
       <c r="AB21" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="46">
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="E10:X10"/>
@@ -5429,6 +5424,7 @@
     <mergeCell ref="M11:P11"/>
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
+    <mergeCell ref="S3:X3"/>
     <mergeCell ref="U12:X12"/>
     <mergeCell ref="Y12:AB12"/>
     <mergeCell ref="A13:D13"/>

--- a/wwwroot/ExcelModel/Primark_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Primark_PHY_sheet.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D147BA0-C9B0-46D1-BFCC-605A340DEC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E10A608-7077-4BDB-80D0-2EBCE20461AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
     <sheet name="Wicking" sheetId="40" r:id="rId2"/>
     <sheet name="Accelerotor" sheetId="36" r:id="rId3"/>
-    <sheet name="Absorbency" sheetId="31" r:id="rId4"/>
-    <sheet name="ASTM F963-23" sheetId="42" r:id="rId5"/>
+    <sheet name="ASTM F963-23" sheetId="42" r:id="rId4"/>
+    <sheet name="Absorbency" sheetId="31" r:id="rId5"/>
     <sheet name="Attachment Strength" sheetId="32" r:id="rId6"/>
     <sheet name="Torque&amp;Tension" sheetId="53" r:id="rId7"/>
     <sheet name="PM03PM05" sheetId="54" r:id="rId8"/>
@@ -43,10 +43,10 @@
   </sheets>
   <definedNames>
     <definedName name="ReportNumber" localSheetId="12">Abrasion!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="3">Absorbency!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="4">Absorbency!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="2">Accelerotor!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="22">'Air Permeability'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="4">'ASTM F963-23'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="3">'ASTM F963-23'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="5">'Attachment Strength'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="18">'Bursting Strength'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="19">'Bursting Strength-G'!$M$1</definedName>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="472">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>□Original      □After washing</t>
-  </si>
-  <si>
-    <t>AATCC TM201-2012(2014)e3</t>
   </si>
   <si>
     <t>Test Condition:</t>
@@ -318,9 +315,6 @@
   </si>
   <si>
     <t>Attachment Strength of Snaps</t>
-  </si>
-  <si>
-    <t>ASTM F963-23</t>
   </si>
   <si>
     <t>Requirement:</t>
@@ -2743,9 +2737,6 @@
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
-    <t>BS EN ISO 2411:2024</t>
-  </si>
-  <si>
     <t xml:space="preserve">*3The fabric_______ before achieving the maximum loading, so the width of seam opening can’t be measured, only reports the </t>
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
@@ -2831,10 +2822,6 @@
   </si>
   <si>
     <t>Hydrostatic head Test</t>
-    <phoneticPr fontId="41" type="noConversion"/>
-  </si>
-  <si>
-    <t>BS EN 13770:2002</t>
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
@@ -4810,7 +4797,7 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
@@ -4869,7 +4856,7 @@
     </row>
     <row r="4" spans="1:28" ht="16.2">
       <c r="A4" s="24" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="24"/>
@@ -4898,7 +4885,7 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="24" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="24"/>
@@ -4927,7 +4914,7 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="24"/>
@@ -4956,7 +4943,7 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
@@ -5012,14 +4999,14 @@
     </row>
     <row r="9" spans="1:28" ht="16.2">
       <c r="A9" s="24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
       <c r="G9" s="24"/>
       <c r="H9" s="24"/>
       <c r="I9" s="24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J9" s="24"/>
       <c r="K9" s="24"/>
@@ -5049,7 +5036,7 @@
       <c r="C10" s="139"/>
       <c r="D10" s="140"/>
       <c r="E10" s="132" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F10" s="133"/>
       <c r="G10" s="133"/>
@@ -5071,7 +5058,7 @@
       <c r="W10" s="133"/>
       <c r="X10" s="133"/>
       <c r="Y10" s="144" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Z10" s="145"/>
       <c r="AA10" s="145"/>
@@ -5083,31 +5070,31 @@
       <c r="C11" s="142"/>
       <c r="D11" s="143"/>
       <c r="E11" s="132" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="133"/>
       <c r="G11" s="133"/>
       <c r="H11" s="134"/>
       <c r="I11" s="132" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="133"/>
       <c r="K11" s="133"/>
       <c r="L11" s="134"/>
       <c r="M11" s="132" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" s="133"/>
       <c r="O11" s="133"/>
       <c r="P11" s="134"/>
       <c r="Q11" s="132" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R11" s="133"/>
       <c r="S11" s="133"/>
       <c r="T11" s="134"/>
       <c r="U11" s="132" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="V11" s="133"/>
       <c r="W11" s="133"/>
@@ -5269,7 +5256,7 @@
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -5509,7 +5496,7 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="54" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B2" s="114"/>
       <c r="C2" s="114"/>
@@ -5534,12 +5521,12 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="20" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -5547,7 +5534,7 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="27" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -5555,7 +5542,7 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -5563,12 +5550,12 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="14.4">
       <c r="A13" s="209" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B13" s="210"/>
       <c r="C13" s="210"/>
@@ -5577,7 +5564,7 @@
       <c r="F13" s="203"/>
       <c r="G13" s="204"/>
       <c r="H13" s="201" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I13" s="202"/>
       <c r="J13" s="202"/>
@@ -5586,7 +5573,7 @@
       <c r="M13" s="202"/>
       <c r="N13" s="205"/>
       <c r="O13" s="201" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="P13" s="202"/>
       <c r="Q13" s="202"/>
@@ -5595,7 +5582,7 @@
       <c r="T13" s="202"/>
       <c r="U13" s="205"/>
       <c r="V13" s="202" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="W13" s="202"/>
       <c r="X13" s="202"/>
@@ -5606,7 +5593,7 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="195" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B14" s="195"/>
       <c r="C14" s="195"/>
@@ -5638,7 +5625,7 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="195" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B15" s="195"/>
       <c r="C15" s="195"/>
@@ -5670,12 +5657,12 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="28" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="28" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -5683,12 +5670,12 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="28" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="54" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -5696,12 +5683,12 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="20" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -5709,7 +5696,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="27" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -5717,7 +5704,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="20" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -5725,12 +5712,12 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="14.4">
       <c r="A33" s="209" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B33" s="210"/>
       <c r="C33" s="210"/>
@@ -5739,39 +5726,39 @@
       <c r="F33" s="203"/>
       <c r="G33" s="204"/>
       <c r="H33" s="200" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I33" s="200"/>
       <c r="J33" s="200"/>
       <c r="K33" s="200" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L33" s="200"/>
       <c r="M33" s="200"/>
       <c r="N33" s="200" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="O33" s="200"/>
       <c r="P33" s="200"/>
       <c r="Q33" s="200" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="R33" s="200"/>
       <c r="S33" s="200"/>
       <c r="T33" s="200" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="U33" s="200"/>
       <c r="V33" s="200"/>
       <c r="W33" s="200" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="X33" s="200"/>
       <c r="Y33" s="200"/>
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="195" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B34" s="195"/>
       <c r="C34" s="195"/>
@@ -5800,7 +5787,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="195" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B35" s="195"/>
       <c r="C35" s="195"/>
@@ -5829,12 +5816,12 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="28" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="28" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -5842,7 +5829,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="28" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -5938,7 +5925,7 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="54" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B2" s="114"/>
       <c r="C2" s="114"/>
@@ -5951,7 +5938,7 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="115" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -5959,17 +5946,17 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="116" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="42" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -5977,12 +5964,12 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="117" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="42" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -5990,7 +5977,7 @@
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="42" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="16.2" customHeight="1">
@@ -6005,12 +5992,12 @@
       <c r="G14" s="203"/>
       <c r="H14" s="204"/>
       <c r="I14" s="205" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J14" s="200"/>
       <c r="K14" s="200"/>
       <c r="L14" s="216" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M14" s="216"/>
       <c r="N14" s="216"/>
@@ -6019,7 +6006,7 @@
       <c r="Q14" s="216"/>
       <c r="R14" s="216"/>
       <c r="S14" s="216" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="T14" s="216"/>
       <c r="U14" s="216"/>
@@ -6030,12 +6017,12 @@
     </row>
     <row r="15" spans="1:28" ht="13.8" customHeight="1">
       <c r="A15" s="212" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B15" s="212"/>
       <c r="C15" s="212"/>
       <c r="D15" s="212" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E15" s="215"/>
       <c r="F15" s="215"/>
@@ -6066,7 +6053,7 @@
       <c r="B16" s="212"/>
       <c r="C16" s="212"/>
       <c r="D16" s="212" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E16" s="212"/>
       <c r="F16" s="212"/>
@@ -6095,7 +6082,7 @@
       <c r="B17" s="212"/>
       <c r="C17" s="212"/>
       <c r="D17" s="212" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E17" s="212"/>
       <c r="F17" s="212"/>
@@ -6124,7 +6111,7 @@
       <c r="B18" s="212"/>
       <c r="C18" s="212"/>
       <c r="D18" s="212" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E18" s="212"/>
       <c r="F18" s="212"/>
@@ -6153,7 +6140,7 @@
       <c r="B19" s="212"/>
       <c r="C19" s="212"/>
       <c r="D19" s="212" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E19" s="212"/>
       <c r="F19" s="212"/>
@@ -6182,7 +6169,7 @@
       <c r="B20" s="212"/>
       <c r="C20" s="212"/>
       <c r="D20" s="212" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E20" s="212"/>
       <c r="F20" s="212"/>
@@ -6208,12 +6195,12 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="212" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B21" s="212"/>
       <c r="C21" s="212"/>
       <c r="D21" s="212" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E21" s="212"/>
       <c r="F21" s="212"/>
@@ -6242,7 +6229,7 @@
       <c r="B22" s="212"/>
       <c r="C22" s="212"/>
       <c r="D22" s="212" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E22" s="212"/>
       <c r="F22" s="212"/>
@@ -6271,7 +6258,7 @@
       <c r="B23" s="212"/>
       <c r="C23" s="212"/>
       <c r="D23" s="212" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E23" s="212"/>
       <c r="F23" s="212"/>
@@ -6300,7 +6287,7 @@
       <c r="B24" s="212"/>
       <c r="C24" s="212"/>
       <c r="D24" s="212" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E24" s="212"/>
       <c r="F24" s="212"/>
@@ -6329,7 +6316,7 @@
       <c r="B25" s="212"/>
       <c r="C25" s="212"/>
       <c r="D25" s="212" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E25" s="212"/>
       <c r="F25" s="212"/>
@@ -6358,7 +6345,7 @@
       <c r="B26" s="212"/>
       <c r="C26" s="212"/>
       <c r="D26" s="212" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E26" s="212"/>
       <c r="F26" s="212"/>
@@ -6384,7 +6371,7 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="42" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -6394,22 +6381,22 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="52" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="42" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="42" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="42" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:28">
@@ -6417,7 +6404,7 @@
     </row>
     <row r="35" spans="1:28">
       <c r="A35" s="42" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="36" spans="1:28">
@@ -6425,12 +6412,12 @@
     </row>
     <row r="37" spans="1:28">
       <c r="A37" s="42" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="200" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -6439,7 +6426,7 @@
       <c r="F39" s="200"/>
       <c r="G39" s="200"/>
       <c r="H39" s="200" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I39" s="200"/>
       <c r="J39" s="200"/>
@@ -6456,7 +6443,7 @@
       <c r="U39" s="200"/>
       <c r="V39" s="200"/>
       <c r="W39" s="200" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="X39" s="200"/>
       <c r="Y39" s="200"/>
@@ -6473,27 +6460,27 @@
       <c r="F40" s="200"/>
       <c r="G40" s="200"/>
       <c r="H40" s="200" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I40" s="200"/>
       <c r="J40" s="200"/>
       <c r="K40" s="200" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L40" s="200"/>
       <c r="M40" s="200"/>
       <c r="N40" s="200" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="O40" s="200"/>
       <c r="P40" s="200"/>
       <c r="Q40" s="200" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="R40" s="200"/>
       <c r="S40" s="200"/>
       <c r="T40" s="200" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="U40" s="200"/>
       <c r="V40" s="200"/>
@@ -6509,7 +6496,7 @@
       <c r="B41" s="211"/>
       <c r="C41" s="211"/>
       <c r="D41" s="200" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E41" s="200"/>
       <c r="F41" s="200"/>
@@ -6541,7 +6528,7 @@
       <c r="B42" s="211"/>
       <c r="C42" s="211"/>
       <c r="D42" s="200" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E42" s="200"/>
       <c r="F42" s="200"/>
@@ -6573,7 +6560,7 @@
       <c r="B43" s="211"/>
       <c r="C43" s="211"/>
       <c r="D43" s="200" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E43" s="200"/>
       <c r="F43" s="200"/>
@@ -6605,7 +6592,7 @@
       <c r="B44" s="211"/>
       <c r="C44" s="211"/>
       <c r="D44" s="200" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E44" s="200"/>
       <c r="F44" s="200"/>
@@ -6637,7 +6624,7 @@
       <c r="B45" s="211"/>
       <c r="C45" s="211"/>
       <c r="D45" s="200" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E45" s="200"/>
       <c r="F45" s="200"/>
@@ -6669,7 +6656,7 @@
       <c r="B46" s="211"/>
       <c r="C46" s="211"/>
       <c r="D46" s="200" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E46" s="200"/>
       <c r="F46" s="200"/>
@@ -6874,7 +6861,7 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -6896,17 +6883,17 @@
     </row>
     <row r="4" spans="1:38">
       <c r="A4" s="71" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:38">
       <c r="A6" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:38">
       <c r="A7" s="220" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" s="188"/>
       <c r="C7" s="188"/>
@@ -6922,7 +6909,7 @@
       <c r="M7" s="188"/>
       <c r="N7" s="188"/>
       <c r="O7" s="217" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P7" s="218"/>
       <c r="Q7" s="218"/>
@@ -7030,7 +7017,7 @@
     </row>
     <row r="10" spans="1:38">
       <c r="A10" s="188" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B10" s="188"/>
       <c r="C10" s="188"/>
@@ -7112,7 +7099,7 @@
     </row>
     <row r="12" spans="1:38">
       <c r="A12" s="188" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" s="188"/>
       <c r="C12" s="188"/>
@@ -7194,18 +7181,18 @@
     </row>
     <row r="15" spans="1:38">
       <c r="A15" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B15" s="21"/>
       <c r="F15" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
     </row>
     <row r="16" spans="1:38">
       <c r="A16" s="220" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B16" s="188"/>
       <c r="C16" s="188"/>
@@ -7221,7 +7208,7 @@
       <c r="M16" s="188"/>
       <c r="N16" s="188"/>
       <c r="O16" s="217" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P16" s="218"/>
       <c r="Q16" s="218"/>
@@ -7329,7 +7316,7 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="188" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B19" s="188"/>
       <c r="C19" s="188"/>
@@ -7411,7 +7398,7 @@
     </row>
     <row r="21" spans="1:38">
       <c r="A21" s="188" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -7588,7 +7575,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="225" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2" s="225"/>
       <c r="C2" s="225"/>
@@ -7710,14 +7697,14 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="165"/>
       <c r="D5" s="165"/>
       <c r="E5" s="165"/>
       <c r="F5" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -7734,7 +7721,7 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="120" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
@@ -7796,7 +7783,7 @@
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -7880,7 +7867,7 @@
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1">
       <c r="A9" s="170" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B9" s="170"/>
       <c r="C9" s="170"/>
@@ -7962,7 +7949,7 @@
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7984,7 +7971,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
@@ -8009,7 +7996,7 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -8028,7 +8015,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
@@ -8053,7 +8040,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -8072,7 +8059,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
@@ -8097,7 +8084,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -8116,7 +8103,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
@@ -8141,7 +8128,7 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -8160,7 +8147,7 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
@@ -8185,7 +8172,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -8346,7 +8333,7 @@
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1">
       <c r="A20" s="225" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" s="225"/>
       <c r="C20" s="225"/>
@@ -8365,19 +8352,7 @@
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="65" t="s">
-        <v>469</v>
-      </c>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
+      <c r="T20" s="72"/>
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
@@ -8470,7 +8445,7 @@
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -8552,14 +8527,14 @@
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="165"/>
       <c r="D25" s="165"/>
       <c r="E25" s="165"/>
       <c r="F25" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -8636,7 +8611,7 @@
     </row>
     <row r="27" spans="1:38" ht="15" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -8891,7 +8866,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="54" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
@@ -8924,7 +8899,7 @@
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F3" s="229"/>
       <c r="G3" s="229"/>
@@ -8956,7 +8931,7 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D4" s="131"/>
       <c r="E4" s="131"/>
@@ -8990,7 +8965,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B5" s="24"/>
       <c r="D5" s="24"/>
@@ -9040,13 +9015,13 @@
       <c r="F6" s="208"/>
       <c r="G6" s="208"/>
       <c r="H6" s="208" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I6" s="208"/>
       <c r="J6" s="208"/>
       <c r="K6" s="208"/>
       <c r="L6" s="230" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M6" s="230"/>
       <c r="N6" s="230"/>
@@ -9060,13 +9035,13 @@
       <c r="V6" s="230"/>
       <c r="W6" s="230"/>
       <c r="X6" s="208" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Y6" s="208"/>
       <c r="Z6" s="208"/>
       <c r="AA6" s="208"/>
       <c r="AB6" s="230" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AC6" s="230"/>
       <c r="AD6" s="230"/>
@@ -9092,19 +9067,19 @@
       <c r="J7" s="208"/>
       <c r="K7" s="208"/>
       <c r="L7" s="230" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M7" s="230"/>
       <c r="N7" s="230"/>
       <c r="O7" s="230"/>
       <c r="P7" s="230" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q7" s="230"/>
       <c r="R7" s="230"/>
       <c r="S7" s="230"/>
       <c r="T7" s="230" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="U7" s="230"/>
       <c r="V7" s="230"/>
@@ -9114,19 +9089,19 @@
       <c r="Z7" s="208"/>
       <c r="AA7" s="208"/>
       <c r="AB7" s="230" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AC7" s="230"/>
       <c r="AD7" s="230"/>
       <c r="AE7" s="230"/>
       <c r="AF7" s="230" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG7" s="230"/>
       <c r="AH7" s="230"/>
       <c r="AI7" s="230"/>
       <c r="AJ7" s="230" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AK7" s="230"/>
       <c r="AL7" s="230"/>
@@ -9299,7 +9274,7 @@
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B12" s="24"/>
       <c r="D12" s="24"/>
@@ -9349,13 +9324,13 @@
       <c r="F13" s="208"/>
       <c r="G13" s="208"/>
       <c r="H13" s="208" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I13" s="208"/>
       <c r="J13" s="208"/>
       <c r="K13" s="208"/>
       <c r="L13" s="230" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M13" s="230"/>
       <c r="N13" s="230"/>
@@ -9369,13 +9344,13 @@
       <c r="V13" s="230"/>
       <c r="W13" s="230"/>
       <c r="X13" s="208" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Y13" s="208"/>
       <c r="Z13" s="208"/>
       <c r="AA13" s="208"/>
       <c r="AB13" s="230" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AC13" s="230"/>
       <c r="AD13" s="230"/>
@@ -9401,19 +9376,19 @@
       <c r="J14" s="208"/>
       <c r="K14" s="208"/>
       <c r="L14" s="230" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M14" s="230"/>
       <c r="N14" s="230"/>
       <c r="O14" s="230"/>
       <c r="P14" s="230" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q14" s="230"/>
       <c r="R14" s="230"/>
       <c r="S14" s="230"/>
       <c r="T14" s="230" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="U14" s="230"/>
       <c r="V14" s="230"/>
@@ -9423,19 +9398,19 @@
       <c r="Z14" s="208"/>
       <c r="AA14" s="208"/>
       <c r="AB14" s="230" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AC14" s="230"/>
       <c r="AD14" s="230"/>
       <c r="AE14" s="230"/>
       <c r="AF14" s="230" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG14" s="230"/>
       <c r="AH14" s="230"/>
       <c r="AI14" s="230"/>
       <c r="AJ14" s="230" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AK14" s="230"/>
       <c r="AL14" s="230"/>
@@ -9669,7 +9644,7 @@
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
       <c r="A21" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B21" s="24"/>
       <c r="C21" s="24"/>
@@ -9705,7 +9680,7 @@
     </row>
     <row r="22" spans="1:38" ht="15" customHeight="1">
       <c r="A22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B22" s="59"/>
       <c r="C22" s="59"/>
@@ -9720,7 +9695,7 @@
       <c r="L22" s="59"/>
       <c r="M22" s="59"/>
       <c r="N22" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O22" s="59"/>
       <c r="P22" s="59"/>
@@ -9735,7 +9710,7 @@
       <c r="Y22" s="59"/>
       <c r="Z22" s="59"/>
       <c r="AA22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AB22" s="59"/>
       <c r="AC22" s="59"/>
@@ -9751,7 +9726,7 @@
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H23" s="59"/>
       <c r="I23" s="59"/>
@@ -9761,7 +9736,7 @@
       <c r="M23" s="59"/>
       <c r="N23" s="59"/>
       <c r="O23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P23" s="59"/>
       <c r="Q23" s="59"/>
@@ -9776,7 +9751,7 @@
       <c r="Z23" s="59"/>
       <c r="AA23" s="59"/>
       <c r="AB23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AC23" s="59"/>
       <c r="AD23" s="59"/>
@@ -9824,7 +9799,7 @@
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H25" s="59"/>
       <c r="I25" s="59"/>
@@ -9834,7 +9809,7 @@
       <c r="M25" s="59"/>
       <c r="N25" s="59"/>
       <c r="O25" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P25" s="59"/>
       <c r="Q25" s="59"/>
@@ -9849,7 +9824,7 @@
       <c r="Z25" s="59"/>
       <c r="AA25" s="59"/>
       <c r="AB25" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AC25" s="59"/>
       <c r="AD25" s="59"/>
@@ -9897,7 +9872,7 @@
     </row>
     <row r="27" spans="1:38" ht="15" customHeight="1">
       <c r="A27" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H27" s="59"/>
       <c r="I27" s="59"/>
@@ -9907,7 +9882,7 @@
       <c r="M27" s="59"/>
       <c r="N27" s="59"/>
       <c r="O27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P27" s="59"/>
       <c r="Q27" s="59"/>
@@ -9922,7 +9897,7 @@
       <c r="Z27" s="59"/>
       <c r="AA27" s="59"/>
       <c r="AB27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AC27" s="59"/>
       <c r="AD27" s="59"/>
@@ -9937,7 +9912,7 @@
     </row>
     <row r="28" spans="1:38" ht="15" customHeight="1">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H28" s="59"/>
       <c r="I28" s="59"/>
@@ -9973,7 +9948,7 @@
     </row>
     <row r="29" spans="1:38" ht="15" customHeight="1">
       <c r="A29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H29" s="59"/>
       <c r="I29" s="59"/>
@@ -10049,7 +10024,7 @@
     </row>
     <row r="31" spans="1:38" ht="15" customHeight="1">
       <c r="A31" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B31" s="48"/>
       <c r="C31" s="48"/>
@@ -10065,7 +10040,7 @@
       <c r="M31" s="48"/>
       <c r="N31" s="48"/>
       <c r="O31" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P31" s="48"/>
       <c r="Q31" s="48"/>
@@ -10080,7 +10055,7 @@
       <c r="Z31" s="48"/>
       <c r="AA31" s="48"/>
       <c r="AB31" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AC31" s="48"/>
       <c r="AD31" s="48"/>
@@ -10095,7 +10070,7 @@
     </row>
     <row r="32" spans="1:38" ht="15" customHeight="1">
       <c r="A32" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B32" s="59"/>
       <c r="C32" s="59"/>
@@ -10137,7 +10112,7 @@
     </row>
     <row r="33" spans="1:41" ht="15" customHeight="1">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B33" s="59"/>
       <c r="C33" s="59"/>
@@ -10219,7 +10194,7 @@
     </row>
     <row r="35" spans="1:41" ht="15" customHeight="1">
       <c r="A35" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B35" s="48"/>
       <c r="C35" s="48"/>
@@ -10235,7 +10210,7 @@
       <c r="M35" s="48"/>
       <c r="N35" s="48"/>
       <c r="O35" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="P35" s="59"/>
       <c r="Q35" s="59"/>
@@ -10250,7 +10225,7 @@
       <c r="Z35" s="59"/>
       <c r="AA35" s="59"/>
       <c r="AB35" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AC35" s="59"/>
       <c r="AD35" s="59"/>
@@ -10265,7 +10240,7 @@
     </row>
     <row r="36" spans="1:41" ht="15" customHeight="1">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B36" s="59"/>
       <c r="C36" s="59"/>
@@ -10307,7 +10282,7 @@
     </row>
     <row r="37" spans="1:41" ht="15" customHeight="1">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B37" s="59"/>
       <c r="C37" s="59"/>
@@ -10360,7 +10335,7 @@
     </row>
     <row r="39" spans="1:41" ht="15" customHeight="1">
       <c r="A39" s="97" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B39" s="98"/>
       <c r="C39" s="98"/>
@@ -10402,7 +10377,7 @@
     </row>
     <row r="40" spans="1:41" ht="15" customHeight="1">
       <c r="A40" s="98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B40" s="98"/>
       <c r="C40" s="98"/>
@@ -10412,7 +10387,7 @@
       <c r="G40" s="226"/>
       <c r="H40" s="226"/>
       <c r="I40" s="99" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J40" s="98"/>
       <c r="K40" s="98"/>
@@ -10446,7 +10421,7 @@
     </row>
     <row r="41" spans="1:41" ht="15" customHeight="1">
       <c r="A41" s="98" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B41" s="98"/>
       <c r="C41" s="98"/>
@@ -10477,7 +10452,7 @@
       <c r="AB41" s="228"/>
       <c r="AC41" s="228"/>
       <c r="AD41" s="100" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AE41" s="98"/>
       <c r="AF41" s="98"/>
@@ -10493,7 +10468,7 @@
     </row>
     <row r="42" spans="1:41" ht="15" customHeight="1">
       <c r="A42" s="99" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B42" s="99"/>
       <c r="C42" s="99"/>
@@ -10521,7 +10496,7 @@
       <c r="Y42" s="226"/>
       <c r="Z42" s="226"/>
       <c r="AA42" s="98" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AB42" s="228"/>
       <c r="AC42" s="228"/>
@@ -10530,7 +10505,7 @@
       <c r="AF42" s="228"/>
       <c r="AG42" s="228"/>
       <c r="AH42" s="98" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AI42" s="98"/>
       <c r="AJ42" s="98"/>
@@ -10854,7 +10829,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -11053,25 +11028,25 @@
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="165"/>
       <c r="G7" s="165"/>
       <c r="H7" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L7" s="163"/>
       <c r="M7" s="163"/>
       <c r="N7" s="163"/>
       <c r="O7" s="163"/>
       <c r="P7" s="17" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Q7" s="7"/>
       <c r="R7" s="6"/>
@@ -11134,7 +11109,7 @@
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -11209,7 +11184,7 @@
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -11284,7 +11259,7 @@
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -11360,7 +11335,7 @@
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -11435,7 +11410,7 @@
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -11510,7 +11485,7 @@
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1">
       <c r="A19" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -11585,7 +11560,7 @@
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -11660,7 +11635,7 @@
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -11735,7 +11710,7 @@
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -11810,7 +11785,7 @@
     </row>
     <row r="27" spans="1:38" ht="15" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -11885,7 +11860,7 @@
     </row>
     <row r="29" spans="1:38" ht="15" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -11960,7 +11935,7 @@
     </row>
     <row r="31" spans="1:38" ht="15" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -12035,7 +12010,7 @@
     </row>
     <row r="33" spans="1:38" ht="15" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -12110,7 +12085,7 @@
     </row>
     <row r="35" spans="1:38" ht="15" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -12185,7 +12160,7 @@
     </row>
     <row r="37" spans="1:38" ht="17.100000000000001" customHeight="1">
       <c r="A37" s="233" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B37" s="233"/>
       <c r="C37" s="234"/>
@@ -12197,61 +12172,61 @@
       <c r="G37" s="236"/>
       <c r="H37" s="169"/>
       <c r="I37" s="237" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J37" s="238"/>
       <c r="K37" s="239"/>
       <c r="L37" s="235" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M37" s="236"/>
       <c r="N37" s="236"/>
       <c r="O37" s="169"/>
       <c r="P37" s="235" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q37" s="236"/>
       <c r="R37" s="236"/>
       <c r="S37" s="169"/>
       <c r="T37" s="235" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="U37" s="236"/>
       <c r="V37" s="236"/>
       <c r="W37" s="169"/>
       <c r="X37" s="235" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Y37" s="236"/>
       <c r="Z37" s="236"/>
       <c r="AA37" s="169"/>
       <c r="AB37" s="235" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AC37" s="236"/>
       <c r="AD37" s="236"/>
       <c r="AE37" s="169"/>
       <c r="AF37" s="235" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AG37" s="236"/>
       <c r="AH37" s="236"/>
       <c r="AI37" s="169"/>
       <c r="AJ37" s="235" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AK37" s="236"/>
       <c r="AL37" s="169"/>
     </row>
     <row r="38" spans="1:38" ht="17.100000000000001" customHeight="1">
       <c r="A38" s="175" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B38" s="176"/>
       <c r="C38" s="176"/>
       <c r="D38" s="177"/>
       <c r="E38" s="170" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F38" s="170"/>
       <c r="G38" s="170"/>
@@ -12293,7 +12268,7 @@
       <c r="C39" s="241"/>
       <c r="D39" s="242"/>
       <c r="E39" s="170" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F39" s="170"/>
       <c r="G39" s="170"/>
@@ -12335,7 +12310,7 @@
       <c r="C40" s="241"/>
       <c r="D40" s="242"/>
       <c r="E40" s="170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F40" s="170"/>
       <c r="G40" s="170"/>
@@ -12377,7 +12352,7 @@
       <c r="C41" s="241"/>
       <c r="D41" s="242"/>
       <c r="E41" s="170" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F41" s="170"/>
       <c r="G41" s="170"/>
@@ -12419,7 +12394,7 @@
       <c r="C42" s="241"/>
       <c r="D42" s="242"/>
       <c r="E42" s="170" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F42" s="170"/>
       <c r="G42" s="170"/>
@@ -12499,13 +12474,13 @@
     </row>
     <row r="44" spans="1:38" ht="17.100000000000001" customHeight="1">
       <c r="A44" s="175" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B44" s="176"/>
       <c r="C44" s="176"/>
       <c r="D44" s="177"/>
       <c r="E44" s="170" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F44" s="170"/>
       <c r="G44" s="170"/>
@@ -12547,7 +12522,7 @@
       <c r="C45" s="241"/>
       <c r="D45" s="242"/>
       <c r="E45" s="170" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F45" s="170"/>
       <c r="G45" s="170"/>
@@ -12589,7 +12564,7 @@
       <c r="C46" s="241"/>
       <c r="D46" s="242"/>
       <c r="E46" s="170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F46" s="170"/>
       <c r="G46" s="170"/>
@@ -12631,7 +12606,7 @@
       <c r="C47" s="241"/>
       <c r="D47" s="242"/>
       <c r="E47" s="170" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F47" s="170"/>
       <c r="G47" s="170"/>
@@ -12673,7 +12648,7 @@
       <c r="C48" s="241"/>
       <c r="D48" s="242"/>
       <c r="E48" s="170" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F48" s="170"/>
       <c r="G48" s="170"/>
@@ -12793,7 +12768,7 @@
     </row>
     <row r="51" spans="1:38" ht="15" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -12835,7 +12810,7 @@
     </row>
     <row r="52" spans="1:38" ht="15" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -12877,7 +12852,7 @@
     </row>
     <row r="53" spans="1:38" ht="15" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -12895,7 +12870,7 @@
       <c r="O53" s="7"/>
       <c r="P53" s="7"/>
       <c r="Q53" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="R53" s="7"/>
       <c r="S53" s="6"/>
@@ -12921,7 +12896,7 @@
     </row>
     <row r="54" spans="1:38" ht="15" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -13222,7 +13197,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="252" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B2" s="252"/>
       <c r="C2" s="252"/>
@@ -13286,7 +13261,7 @@
       <c r="U3" s="2"/>
       <c r="W3" s="72"/>
       <c r="AA3" s="84" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AE3" s="179"/>
       <c r="AF3" s="179"/>
@@ -13299,7 +13274,7 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -13341,7 +13316,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="64"/>
@@ -14442,7 +14417,7 @@
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
       <c r="A2" s="43" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -14524,7 +14499,7 @@
     </row>
     <row r="4" spans="1:39" ht="15" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -14566,7 +14541,7 @@
     </row>
     <row r="5" spans="1:39" ht="15" customHeight="1">
       <c r="A5" s="87" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -14608,7 +14583,7 @@
     </row>
     <row r="6" spans="1:39" ht="15" customHeight="1">
       <c r="A6" s="87" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -14650,7 +14625,7 @@
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -14732,7 +14707,7 @@
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -14774,7 +14749,7 @@
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -14816,7 +14791,7 @@
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -14858,7 +14833,7 @@
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
       <c r="A12" s="208" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B12" s="208"/>
       <c r="C12" s="208"/>
@@ -14915,35 +14890,35 @@
       <c r="I13" s="208"/>
       <c r="J13" s="208"/>
       <c r="K13" s="230" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L13" s="230"/>
       <c r="M13" s="230"/>
       <c r="N13" s="230"/>
       <c r="O13" s="230"/>
       <c r="P13" s="230" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="230"/>
       <c r="R13" s="230"/>
       <c r="S13" s="230"/>
       <c r="T13" s="230"/>
       <c r="U13" s="230" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V13" s="230"/>
       <c r="W13" s="230"/>
       <c r="X13" s="230"/>
       <c r="Y13" s="230"/>
       <c r="Z13" s="230" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA13" s="230"/>
       <c r="AB13" s="230"/>
       <c r="AC13" s="230"/>
       <c r="AD13" s="230"/>
       <c r="AE13" s="230" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AF13" s="230"/>
       <c r="AG13" s="230"/>
@@ -14958,7 +14933,7 @@
       <c r="A14" s="190"/>
       <c r="B14" s="192"/>
       <c r="C14" s="253" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D14" s="253"/>
       <c r="E14" s="253"/>
@@ -15001,7 +14976,7 @@
       <c r="A15" s="193"/>
       <c r="B15" s="194"/>
       <c r="C15" s="253" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D15" s="253"/>
       <c r="E15" s="253"/>
@@ -15044,7 +15019,7 @@
       <c r="A16" s="190"/>
       <c r="B16" s="192"/>
       <c r="C16" s="253" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D16" s="253"/>
       <c r="E16" s="253"/>
@@ -15087,7 +15062,7 @@
       <c r="A17" s="193"/>
       <c r="B17" s="194"/>
       <c r="C17" s="253" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D17" s="253"/>
       <c r="E17" s="253"/>
@@ -15130,7 +15105,7 @@
       <c r="A18" s="190"/>
       <c r="B18" s="192"/>
       <c r="C18" s="253" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D18" s="253"/>
       <c r="E18" s="253"/>
@@ -15173,7 +15148,7 @@
       <c r="A19" s="193"/>
       <c r="B19" s="194"/>
       <c r="C19" s="253" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D19" s="253"/>
       <c r="E19" s="253"/>
@@ -15213,7 +15188,7 @@
     </row>
     <row r="20" spans="1:39" ht="15" customHeight="1">
       <c r="A20" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -15255,7 +15230,7 @@
     </row>
     <row r="21" spans="1:39" ht="15" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -15339,7 +15314,7 @@
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1">
       <c r="A23" s="122" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -15381,7 +15356,7 @@
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="44" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -16743,7 +16718,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="54" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
@@ -16790,23 +16765,23 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1"/>
     <row r="6" spans="1:38" ht="15" customHeight="1">
       <c r="A6" s="28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="21.15" customHeight="1">
       <c r="A8" s="36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B8" s="63"/>
       <c r="C8" s="63"/>
@@ -16848,7 +16823,7 @@
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1">
       <c r="A9" s="254" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B9" s="254"/>
       <c r="C9" s="254"/>
@@ -16906,31 +16881,31 @@
       <c r="K10" s="254"/>
       <c r="L10" s="254"/>
       <c r="M10" s="254" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N10" s="254"/>
       <c r="O10" s="254"/>
       <c r="P10" s="254"/>
       <c r="Q10" s="254" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R10" s="254"/>
       <c r="S10" s="254"/>
       <c r="T10" s="254"/>
       <c r="U10" s="254" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V10" s="254"/>
       <c r="W10" s="254"/>
       <c r="X10" s="254"/>
       <c r="Y10" s="254" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z10" s="254"/>
       <c r="AA10" s="254"/>
       <c r="AB10" s="254"/>
       <c r="AC10" s="254" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AD10" s="254"/>
       <c r="AE10" s="254"/>
@@ -16949,7 +16924,7 @@
       <c r="D11" s="259"/>
       <c r="E11" s="260"/>
       <c r="F11" s="255" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G11" s="256"/>
       <c r="H11" s="256"/>
@@ -16991,7 +16966,7 @@
       <c r="D12" s="130"/>
       <c r="E12" s="262"/>
       <c r="F12" s="255" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G12" s="256"/>
       <c r="H12" s="256"/>
@@ -17033,7 +17008,7 @@
       <c r="D13" s="259"/>
       <c r="E13" s="260"/>
       <c r="F13" s="255" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G13" s="256"/>
       <c r="H13" s="256"/>
@@ -17075,7 +17050,7 @@
       <c r="D14" s="130"/>
       <c r="E14" s="262"/>
       <c r="F14" s="255" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G14" s="256"/>
       <c r="H14" s="256"/>
@@ -17117,7 +17092,7 @@
       <c r="D15" s="259"/>
       <c r="E15" s="260"/>
       <c r="F15" s="255" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G15" s="256"/>
       <c r="H15" s="256"/>
@@ -17159,7 +17134,7 @@
       <c r="D16" s="130"/>
       <c r="E16" s="262"/>
       <c r="F16" s="255" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G16" s="256"/>
       <c r="H16" s="256"/>
@@ -17196,7 +17171,7 @@
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1">
       <c r="A17" s="36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
@@ -18725,7 +18700,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="35" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -18764,7 +18739,7 @@
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I3" s="163"/>
       <c r="J3" s="163"/>
@@ -18797,13 +18772,13 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
       <c r="D4" s="39"/>
       <c r="E4" s="88" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F4" s="39"/>
       <c r="G4" s="39"/>
@@ -18841,7 +18816,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
@@ -18972,7 +18947,7 @@
       <c r="C8" s="179"/>
       <c r="D8" s="180"/>
       <c r="E8" s="235" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" s="236"/>
       <c r="G8" s="236"/>
@@ -18980,7 +18955,7 @@
       <c r="I8" s="236"/>
       <c r="J8" s="169"/>
       <c r="K8" s="235" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L8" s="236"/>
       <c r="M8" s="236"/>
@@ -18988,7 +18963,7 @@
       <c r="O8" s="236"/>
       <c r="P8" s="169"/>
       <c r="Q8" s="235" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R8" s="236"/>
       <c r="S8" s="236"/>
@@ -18996,7 +18971,7 @@
       <c r="U8" s="236"/>
       <c r="V8" s="169"/>
       <c r="W8" s="235" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X8" s="236"/>
       <c r="Y8" s="236"/>
@@ -19004,7 +18979,7 @@
       <c r="AA8" s="236"/>
       <c r="AB8" s="169"/>
       <c r="AC8" s="235" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AD8" s="236"/>
       <c r="AE8" s="236"/>
@@ -19138,11 +19113,11 @@
     </row>
     <row r="12" spans="1:38">
       <c r="A12" s="20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B12"/>
       <c r="C12" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -19182,14 +19157,14 @@
     </row>
     <row r="13" spans="1:38">
       <c r="A13" s="42" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
     </row>
     <row r="14" spans="1:38">
       <c r="A14" s="42" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
@@ -19201,12 +19176,12 @@
     </row>
     <row r="17" spans="1:38">
       <c r="A17" s="35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:38">
       <c r="A18" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I18" s="163"/>
       <c r="J18" s="163"/>
@@ -19228,13 +19203,13 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19" s="39"/>
       <c r="C19" s="39"/>
       <c r="D19" s="39"/>
       <c r="E19" s="88" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F19" s="39"/>
       <c r="G19" s="39"/>
@@ -19244,12 +19219,12 @@
     </row>
     <row r="20" spans="1:38">
       <c r="A20" s="84" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:38">
       <c r="A21" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -19260,7 +19235,7 @@
       <c r="C22" s="176"/>
       <c r="D22" s="177"/>
       <c r="E22" s="175" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F22" s="176"/>
       <c r="G22" s="176"/>
@@ -19292,7 +19267,7 @@
       <c r="AG22" s="176"/>
       <c r="AH22" s="177"/>
       <c r="AI22" s="264" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AJ22" s="176"/>
       <c r="AK22" s="176"/>
@@ -19660,22 +19635,22 @@
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -20689,7 +20664,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="46" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -20773,7 +20748,7 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="277" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B4" s="278"/>
       <c r="C4" s="278"/>
@@ -20784,7 +20759,7 @@
       <c r="H4" s="278"/>
       <c r="I4" s="279"/>
       <c r="J4" s="280" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K4" s="281"/>
       <c r="L4" s="281"/>
@@ -20794,7 +20769,7 @@
       <c r="P4" s="281"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="278" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="S4" s="278"/>
       <c r="T4" s="278"/>
@@ -20803,7 +20778,7 @@
       <c r="W4" s="278"/>
       <c r="X4" s="279"/>
       <c r="Y4" s="280" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z4" s="281"/>
       <c r="AA4" s="281"/>
@@ -20813,7 +20788,7 @@
       <c r="AE4" s="281"/>
       <c r="AF4" s="34"/>
       <c r="AG4" s="278" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AH4" s="278"/>
       <c r="AI4" s="278"/>
@@ -21303,7 +21278,7 @@
     </row>
     <row r="17" spans="1:38">
       <c r="A17" s="47" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -21385,7 +21360,7 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="127" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B19" s="128"/>
       <c r="C19" s="128"/>
@@ -21427,7 +21402,7 @@
     </row>
     <row r="20" spans="1:38">
       <c r="A20" s="129" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B20" s="128"/>
       <c r="C20" s="128"/>
@@ -21469,7 +21444,7 @@
     </row>
     <row r="21" spans="1:38">
       <c r="A21" s="127" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B21" s="128"/>
       <c r="C21" s="128"/>
@@ -21510,7 +21485,7 @@
     </row>
     <row r="22" spans="1:38">
       <c r="A22" s="129" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B22" s="128"/>
       <c r="C22" s="128"/>
@@ -21590,7 +21565,7 @@
     </row>
     <row r="24" spans="1:38">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -21744,7 +21719,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="54" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E2" s="24"/>
       <c r="F2" s="24"/>
@@ -21842,7 +21817,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="24"/>
@@ -21906,7 +21881,7 @@
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
@@ -21979,7 +21954,7 @@
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1">
       <c r="A9" s="36" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B9" s="56"/>
       <c r="C9" s="56"/>
@@ -22021,7 +21996,7 @@
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1">
       <c r="A10" s="208" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B10" s="208"/>
       <c r="C10" s="208"/>
@@ -22076,35 +22051,35 @@
       <c r="H11" s="208"/>
       <c r="I11" s="208"/>
       <c r="J11" s="230" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K11" s="230"/>
       <c r="L11" s="230"/>
       <c r="M11" s="230"/>
       <c r="N11" s="230"/>
       <c r="O11" s="230" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P11" s="230"/>
       <c r="Q11" s="230"/>
       <c r="R11" s="230"/>
       <c r="S11" s="230"/>
       <c r="T11" s="230" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U11" s="230"/>
       <c r="V11" s="230"/>
       <c r="W11" s="230"/>
       <c r="X11" s="230"/>
       <c r="Y11" s="230" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z11" s="230"/>
       <c r="AA11" s="230"/>
       <c r="AB11" s="230"/>
       <c r="AC11" s="230"/>
       <c r="AD11" s="230" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AE11" s="230"/>
       <c r="AF11" s="230"/>
@@ -22120,7 +22095,7 @@
       <c r="B12" s="232"/>
       <c r="C12" s="232"/>
       <c r="D12" s="150" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -22162,7 +22137,7 @@
       <c r="B13" s="232"/>
       <c r="C13" s="232"/>
       <c r="D13" s="150" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E13" s="151"/>
       <c r="F13" s="151"/>
@@ -22204,7 +22179,7 @@
       <c r="B14" s="232"/>
       <c r="C14" s="232"/>
       <c r="D14" s="150" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E14" s="151"/>
       <c r="F14" s="151"/>
@@ -22246,7 +22221,7 @@
       <c r="B15" s="232"/>
       <c r="C15" s="232"/>
       <c r="D15" s="150" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E15" s="151"/>
       <c r="F15" s="151"/>
@@ -22285,7 +22260,7 @@
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1">
       <c r="A16" s="283" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B16" s="283"/>
       <c r="C16" s="283"/>
@@ -22367,7 +22342,7 @@
     </row>
     <row r="18" spans="1:39" ht="15" customHeight="1">
       <c r="A18" s="28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
@@ -22409,7 +22384,7 @@
     </row>
     <row r="19" spans="1:39" ht="15" customHeight="1">
       <c r="A19" s="28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
@@ -22442,7 +22417,7 @@
     </row>
     <row r="20" spans="1:39" ht="15" customHeight="1">
       <c r="A20" s="62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
@@ -22475,7 +22450,7 @@
     </row>
     <row r="21" spans="1:39" ht="15" customHeight="1">
       <c r="A21" s="62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
@@ -22508,7 +22483,7 @@
     </row>
     <row r="22" spans="1:39" ht="15" customHeight="1">
       <c r="A22" s="62" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B22" s="86"/>
       <c r="C22" s="86"/>
@@ -22551,7 +22526,7 @@
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1">
       <c r="A23" s="62" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B23" s="86"/>
       <c r="C23" s="86"/>
@@ -23564,7 +23539,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="46" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -23648,7 +23623,7 @@
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1">
       <c r="A4" s="277" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B4" s="278"/>
       <c r="C4" s="278"/>
@@ -23659,7 +23634,7 @@
       <c r="H4" s="278"/>
       <c r="I4" s="279"/>
       <c r="J4" s="280" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K4" s="281"/>
       <c r="L4" s="281"/>
@@ -23669,7 +23644,7 @@
       <c r="P4" s="281"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="278" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="S4" s="278"/>
       <c r="T4" s="278"/>
@@ -23678,7 +23653,7 @@
       <c r="W4" s="278"/>
       <c r="X4" s="279"/>
       <c r="Y4" s="280" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z4" s="281"/>
       <c r="AA4" s="281"/>
@@ -23688,7 +23663,7 @@
       <c r="AE4" s="281"/>
       <c r="AF4" s="34"/>
       <c r="AG4" s="278" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AH4" s="278"/>
       <c r="AI4" s="278"/>
@@ -24178,7 +24153,7 @@
     </row>
     <row r="17" spans="1:38">
       <c r="A17" s="46" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -24262,7 +24237,7 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="277" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B19" s="278"/>
       <c r="C19" s="278"/>
@@ -24273,7 +24248,7 @@
       <c r="H19" s="278"/>
       <c r="I19" s="279"/>
       <c r="J19" s="280" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K19" s="281"/>
       <c r="L19" s="281"/>
@@ -24283,7 +24258,7 @@
       <c r="P19" s="281"/>
       <c r="Q19" s="34"/>
       <c r="R19" s="278" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="S19" s="278"/>
       <c r="T19" s="278"/>
@@ -24292,7 +24267,7 @@
       <c r="W19" s="278"/>
       <c r="X19" s="279"/>
       <c r="Y19" s="280" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z19" s="281"/>
       <c r="AA19" s="281"/>
@@ -24302,7 +24277,7 @@
       <c r="AE19" s="281"/>
       <c r="AF19" s="34"/>
       <c r="AG19" s="278" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AH19" s="278"/>
       <c r="AI19" s="278"/>
@@ -24792,7 +24767,7 @@
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="47" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -24874,7 +24849,7 @@
     </row>
     <row r="34" spans="1:38">
       <c r="A34" s="127" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B34" s="128"/>
       <c r="C34" s="128"/>
@@ -24916,7 +24891,7 @@
     </row>
     <row r="35" spans="1:38">
       <c r="A35" s="129" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B35" s="128"/>
       <c r="C35" s="128"/>
@@ -24958,7 +24933,7 @@
     </row>
     <row r="36" spans="1:38">
       <c r="A36" s="127" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B36" s="128"/>
       <c r="C36" s="128"/>
@@ -25000,7 +24975,7 @@
     </row>
     <row r="37" spans="1:38">
       <c r="A37" s="129" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B37" s="128"/>
       <c r="C37" s="128"/>
@@ -25082,7 +25057,7 @@
     </row>
     <row r="39" spans="1:38">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -25283,7 +25258,7 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -25401,7 +25376,7 @@
     </row>
     <row r="5" spans="1:38" ht="14.4">
       <c r="A5" s="20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="5"/>
@@ -25414,7 +25389,7 @@
       <c r="J5" s="284"/>
       <c r="K5" s="284"/>
       <c r="L5" s="20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
@@ -25445,7 +25420,7 @@
     </row>
     <row r="6" spans="1:38" ht="14.4">
       <c r="A6" s="20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="5"/>
@@ -25458,7 +25433,7 @@
       <c r="J6" s="284"/>
       <c r="K6" s="284"/>
       <c r="L6" s="20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
@@ -25489,7 +25464,7 @@
     </row>
     <row r="7" spans="1:38" ht="14.4">
       <c r="A7" s="20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B7"/>
       <c r="C7" s="11"/>
@@ -25571,7 +25546,7 @@
     </row>
     <row r="9" spans="1:38">
       <c r="A9" s="20" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -25613,7 +25588,7 @@
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1">
       <c r="A10" s="31" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="33"/>
@@ -25621,7 +25596,7 @@
       <c r="E10" s="275"/>
       <c r="F10" s="275"/>
       <c r="G10" s="289" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H10" s="290"/>
       <c r="I10" s="276"/>
@@ -25657,7 +25632,7 @@
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1">
       <c r="A11" s="287" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="287"/>
       <c r="C11" s="288"/>
@@ -25699,7 +25674,7 @@
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1">
       <c r="A12" s="287" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="287"/>
       <c r="C12" s="287"/>
@@ -25741,7 +25716,7 @@
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1">
       <c r="A13" s="287" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="287"/>
       <c r="C13" s="287"/>
@@ -25783,7 +25758,7 @@
     </row>
     <row r="14" spans="1:38" ht="18" customHeight="1">
       <c r="A14" s="287" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B14" s="287"/>
       <c r="C14" s="287"/>
@@ -25825,7 +25800,7 @@
     </row>
     <row r="15" spans="1:38" ht="18" customHeight="1">
       <c r="A15" s="287" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B15" s="287"/>
       <c r="C15" s="287"/>
@@ -25867,7 +25842,7 @@
     </row>
     <row r="16" spans="1:38" ht="18" customHeight="1">
       <c r="A16" s="287" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B16" s="287"/>
       <c r="C16" s="287"/>
@@ -25909,7 +25884,7 @@
     </row>
     <row r="17" spans="1:38" ht="18" customHeight="1">
       <c r="A17" s="287" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B17" s="287"/>
       <c r="C17" s="287"/>
@@ -25951,7 +25926,7 @@
     </row>
     <row r="18" spans="1:38" ht="18" customHeight="1">
       <c r="A18" s="287" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B18" s="287"/>
       <c r="C18" s="287"/>
@@ -25993,7 +25968,7 @@
     </row>
     <row r="19" spans="1:38" ht="18" customHeight="1">
       <c r="A19" s="287" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B19" s="287"/>
       <c r="C19" s="287"/>
@@ -26035,7 +26010,7 @@
     </row>
     <row r="20" spans="1:38" ht="18" customHeight="1">
       <c r="A20" s="287" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B20" s="287"/>
       <c r="C20" s="287"/>
@@ -26119,7 +26094,7 @@
     </row>
     <row r="22" spans="1:38" ht="18" customHeight="1">
       <c r="A22" s="287" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B22" s="287"/>
       <c r="C22" s="287"/>
@@ -26161,12 +26136,12 @@
     </row>
     <row r="23" spans="1:38" ht="14.4">
       <c r="A23" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:38">
       <c r="A24" s="170" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B24" s="170"/>
       <c r="C24" s="170"/>
@@ -26176,7 +26151,7 @@
       <c r="G24" s="170"/>
       <c r="H24" s="170"/>
       <c r="I24" s="171" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J24" s="171"/>
       <c r="K24" s="171"/>
@@ -26184,7 +26159,7 @@
       <c r="M24" s="171"/>
       <c r="N24" s="171"/>
       <c r="O24" s="170" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P24" s="170"/>
       <c r="Q24" s="170"/>
@@ -26200,7 +26175,7 @@
       <c r="AA24" s="170"/>
       <c r="AB24" s="170"/>
       <c r="AC24" s="170" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AD24" s="170"/>
       <c r="AE24" s="170"/>
@@ -26230,7 +26205,7 @@
       <c r="M25" s="170"/>
       <c r="N25" s="170"/>
       <c r="O25" s="235" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P25" s="236"/>
       <c r="Q25" s="236"/>
@@ -26248,7 +26223,7 @@
       <c r="AA25" s="236"/>
       <c r="AB25" s="169"/>
       <c r="AC25" s="170" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AD25" s="170"/>
       <c r="AE25" s="170"/>
@@ -26276,7 +26251,7 @@
       <c r="M26" s="170"/>
       <c r="N26" s="170"/>
       <c r="O26" s="235" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P26" s="236"/>
       <c r="Q26" s="236"/>
@@ -26475,7 +26450,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="92" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B2" s="93"/>
       <c r="C2" s="93"/>
@@ -26531,7 +26506,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="95" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R5" s="95"/>
     </row>
@@ -26545,7 +26520,7 @@
       <c r="E6" s="295"/>
       <c r="F6" s="296"/>
       <c r="G6" s="300" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H6" s="301"/>
       <c r="I6" s="301"/>
@@ -26587,7 +26562,7 @@
       <c r="E7" s="298"/>
       <c r="F7" s="299"/>
       <c r="G7" s="303" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H7" s="303"/>
       <c r="I7" s="303"/>
@@ -26600,7 +26575,7 @@
       <c r="P7" s="303"/>
       <c r="Q7" s="303"/>
       <c r="R7" s="303" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="S7" s="303"/>
       <c r="T7" s="303"/>
@@ -26613,7 +26588,7 @@
       <c r="AA7" s="303"/>
       <c r="AB7" s="303"/>
       <c r="AC7" s="303" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AD7" s="303"/>
       <c r="AE7" s="303"/>
@@ -26747,7 +26722,7 @@
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1">
       <c r="A11" s="121" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="R11" s="95"/>
     </row>
@@ -26761,7 +26736,7 @@
       <c r="E12" s="295"/>
       <c r="F12" s="296"/>
       <c r="G12" s="300" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H12" s="301"/>
       <c r="I12" s="301"/>
@@ -26803,7 +26778,7 @@
       <c r="E13" s="298"/>
       <c r="F13" s="299"/>
       <c r="G13" s="303" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H13" s="303"/>
       <c r="I13" s="303"/>
@@ -26816,7 +26791,7 @@
       <c r="P13" s="303"/>
       <c r="Q13" s="303"/>
       <c r="R13" s="303" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="S13" s="303"/>
       <c r="T13" s="303"/>
@@ -26829,7 +26804,7 @@
       <c r="AA13" s="303"/>
       <c r="AB13" s="303"/>
       <c r="AC13" s="303" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AD13" s="303"/>
       <c r="AE13" s="303"/>
@@ -27003,17 +26978,17 @@
     </row>
     <row r="18" spans="1:39" s="98" customFormat="1" ht="14.1" customHeight="1">
       <c r="A18" s="97" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:39" s="98" customFormat="1">
       <c r="A19" s="98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G19" s="226"/>
       <c r="H19" s="226"/>
       <c r="I19" s="99" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ19" s="227"/>
       <c r="AK19" s="227"/>
@@ -27021,7 +26996,7 @@
     </row>
     <row r="20" spans="1:39" s="98" customFormat="1">
       <c r="A20" s="98" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P20" s="227"/>
       <c r="Q20" s="227"/>
@@ -27035,12 +27010,12 @@
       <c r="Y20" s="227"/>
       <c r="Z20" s="227"/>
       <c r="AA20" s="100" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21" spans="1:39" s="98" customFormat="1">
       <c r="A21" s="99" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B21" s="99"/>
       <c r="C21" s="99"/>
@@ -27067,7 +27042,7 @@
       <c r="Y21" s="305"/>
       <c r="Z21" s="305"/>
       <c r="AA21" s="98" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AB21" s="228"/>
       <c r="AC21" s="228"/>
@@ -27076,7 +27051,7 @@
       <c r="AF21" s="228"/>
       <c r="AG21" s="228"/>
       <c r="AH21" s="98" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:39" s="98" customFormat="1">
@@ -27108,96 +27083,96 @@
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1">
       <c r="A23" s="90" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:39" ht="15" customHeight="1">
       <c r="A24" s="102" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="U24" s="102" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:39" ht="15" customHeight="1">
       <c r="B25" s="102" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="W25" s="102" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:39" ht="15" customHeight="1">
       <c r="B26" s="102" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="W26" s="102" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="1:39" ht="15" customHeight="1">
       <c r="B27" s="102" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="X27" s="102" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AM27" s="103"/>
     </row>
     <row r="28" spans="1:39" ht="15" customHeight="1">
       <c r="B28" s="102" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="W28" s="102" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AM28" s="103"/>
     </row>
     <row r="29" spans="1:39" ht="15" customHeight="1">
       <c r="B29" s="102" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="W29" s="102" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM29" s="103"/>
     </row>
     <row r="30" spans="1:39" ht="15" customHeight="1">
       <c r="C30" s="102" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="X30" s="102" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AM30" s="103"/>
     </row>
     <row r="31" spans="1:39" ht="15" customHeight="1">
       <c r="B31" s="102" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="W31" s="102" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:39" ht="15" customHeight="1">
       <c r="X32" s="102" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="15" customHeight="1">
       <c r="A33" s="104"/>
       <c r="W33" s="102" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="15" customHeight="1">
       <c r="X34" s="102" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="15" customHeight="1">
       <c r="A35" s="104" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15" customHeight="1"/>
@@ -27349,7 +27324,7 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -27467,7 +27442,7 @@
     </row>
     <row r="5" spans="1:38">
       <c r="A5" s="306" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B5" s="306"/>
       <c r="C5" s="306"/>
@@ -27589,7 +27564,7 @@
     </row>
     <row r="8" spans="1:38" ht="14.4">
       <c r="A8" s="27" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -27602,7 +27577,7 @@
       <c r="J8" s="308"/>
       <c r="K8" s="308"/>
       <c r="L8" s="20" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
@@ -27623,7 +27598,7 @@
       <c r="AC8" s="20"/>
       <c r="AD8" s="20"/>
       <c r="AE8" s="20" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AF8" s="20"/>
       <c r="AG8" s="20"/>
@@ -27643,7 +27618,7 @@
       <c r="E9" s="200"/>
       <c r="F9" s="200"/>
       <c r="G9" s="200" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H9" s="200"/>
       <c r="I9" s="200"/>
@@ -27695,31 +27670,31 @@
       <c r="K10" s="200"/>
       <c r="L10" s="200"/>
       <c r="M10" s="200" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N10" s="200"/>
       <c r="O10" s="200"/>
       <c r="P10" s="200"/>
       <c r="Q10" s="200" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R10" s="200"/>
       <c r="S10" s="200"/>
       <c r="T10" s="200"/>
       <c r="U10" s="200" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V10" s="200"/>
       <c r="W10" s="200"/>
       <c r="X10" s="200"/>
       <c r="Y10" s="200" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z10" s="200"/>
       <c r="AA10" s="200"/>
       <c r="AB10" s="200"/>
       <c r="AC10" s="200" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AD10" s="200"/>
       <c r="AE10" s="200"/>
@@ -27739,7 +27714,7 @@
       <c r="E11" s="211"/>
       <c r="F11" s="211"/>
       <c r="G11" s="200" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H11" s="200"/>
       <c r="I11" s="200"/>
@@ -27781,7 +27756,7 @@
       <c r="E12" s="211"/>
       <c r="F12" s="211"/>
       <c r="G12" s="200" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H12" s="200"/>
       <c r="I12" s="200"/>
@@ -27823,7 +27798,7 @@
       <c r="E13" s="211"/>
       <c r="F13" s="211"/>
       <c r="G13" s="200" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H13" s="200"/>
       <c r="I13" s="200"/>
@@ -27865,7 +27840,7 @@
       <c r="E14" s="309"/>
       <c r="F14" s="309"/>
       <c r="G14" s="200" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H14" s="200"/>
       <c r="I14" s="200"/>
@@ -27901,7 +27876,7 @@
     </row>
     <row r="15" spans="1:38" ht="12.6" customHeight="1">
       <c r="A15" s="125" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B15" s="124"/>
       <c r="C15" s="124"/>
@@ -27914,7 +27889,7 @@
       <c r="J15" s="308"/>
       <c r="K15" s="308"/>
       <c r="L15" s="20" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -27935,7 +27910,7 @@
       <c r="AC15" s="126"/>
       <c r="AD15" s="126"/>
       <c r="AE15" s="20" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AF15" s="126"/>
       <c r="AG15" s="124"/>
@@ -27955,7 +27930,7 @@
       <c r="E16" s="200"/>
       <c r="F16" s="200"/>
       <c r="G16" s="200" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H16" s="200"/>
       <c r="I16" s="200"/>
@@ -28007,31 +27982,31 @@
       <c r="K17" s="200"/>
       <c r="L17" s="200"/>
       <c r="M17" s="200" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N17" s="200"/>
       <c r="O17" s="200"/>
       <c r="P17" s="200"/>
       <c r="Q17" s="200" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R17" s="200"/>
       <c r="S17" s="200"/>
       <c r="T17" s="200"/>
       <c r="U17" s="200" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V17" s="200"/>
       <c r="W17" s="200"/>
       <c r="X17" s="200"/>
       <c r="Y17" s="200" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z17" s="200"/>
       <c r="AA17" s="200"/>
       <c r="AB17" s="200"/>
       <c r="AC17" s="200" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AD17" s="200"/>
       <c r="AE17" s="200"/>
@@ -28051,7 +28026,7 @@
       <c r="E18" s="211"/>
       <c r="F18" s="211"/>
       <c r="G18" s="200" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H18" s="200"/>
       <c r="I18" s="200"/>
@@ -28093,7 +28068,7 @@
       <c r="E19" s="211"/>
       <c r="F19" s="211"/>
       <c r="G19" s="200" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H19" s="200"/>
       <c r="I19" s="200"/>
@@ -28135,7 +28110,7 @@
       <c r="E20" s="211"/>
       <c r="F20" s="211"/>
       <c r="G20" s="200" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H20" s="200"/>
       <c r="I20" s="200"/>
@@ -28177,7 +28152,7 @@
       <c r="E21" s="211"/>
       <c r="F21" s="211"/>
       <c r="G21" s="200" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H21" s="200"/>
       <c r="I21" s="200"/>
@@ -28213,7 +28188,7 @@
     </row>
     <row r="22" spans="1:38" ht="18" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -28255,7 +28230,7 @@
     </row>
     <row r="23" spans="1:38" ht="16.2" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B23" s="82"/>
       <c r="C23" s="82"/>
@@ -28297,7 +28272,7 @@
     </row>
     <row r="24" spans="1:38" ht="11.4" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B24" s="82"/>
       <c r="C24" s="82"/>
@@ -28339,7 +28314,7 @@
     </row>
     <row r="25" spans="1:38">
       <c r="A25" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -28381,7 +28356,7 @@
     </row>
     <row r="26" spans="1:38">
       <c r="A26" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -28423,7 +28398,7 @@
     </row>
     <row r="27" spans="1:38">
       <c r="A27" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -28465,7 +28440,7 @@
     </row>
     <row r="28" spans="1:38">
       <c r="A28" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -28547,7 +28522,7 @@
     </row>
     <row r="30" spans="1:38">
       <c r="A30" s="97" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B30" s="98"/>
       <c r="C30" s="98"/>
@@ -28589,7 +28564,7 @@
     </row>
     <row r="31" spans="1:38">
       <c r="A31" s="98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B31" s="98"/>
       <c r="C31" s="98"/>
@@ -28599,7 +28574,7 @@
       <c r="G31" s="226"/>
       <c r="H31" s="226"/>
       <c r="I31" s="99" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J31" s="98"/>
       <c r="K31" s="98"/>
@@ -28633,7 +28608,7 @@
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="98" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B32" s="98"/>
       <c r="C32" s="98"/>
@@ -28661,7 +28636,7 @@
       <c r="Y32" s="227"/>
       <c r="Z32" s="227"/>
       <c r="AA32" s="100" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AB32" s="98"/>
       <c r="AC32" s="98"/>
@@ -28677,7 +28652,7 @@
     </row>
     <row r="33" spans="1:38">
       <c r="A33" s="99" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B33" s="99"/>
       <c r="C33" s="99"/>
@@ -28705,7 +28680,7 @@
       <c r="Y33" s="305"/>
       <c r="Z33" s="305"/>
       <c r="AA33" s="98" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AB33" s="228"/>
       <c r="AC33" s="228"/>
@@ -28714,7 +28689,7 @@
       <c r="AF33" s="228"/>
       <c r="AG33" s="228"/>
       <c r="AH33" s="98" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AI33" s="98"/>
       <c r="AJ33" s="98"/>
@@ -29924,7 +29899,7 @@
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -29989,9 +29964,7 @@
       <c r="X3" s="30"/>
       <c r="Y3" s="30"/>
       <c r="Z3" s="30"/>
-      <c r="AA3" s="30" t="s">
-        <v>458</v>
-      </c>
+      <c r="AA3" s="30"/>
       <c r="AB3" s="30"/>
       <c r="AC3" s="30"/>
       <c r="AD3" s="30"/>
@@ -30048,7 +30021,7 @@
     </row>
     <row r="5" spans="1:39">
       <c r="A5" s="20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -30056,7 +30029,7 @@
     </row>
     <row r="7" spans="1:39">
       <c r="A7" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:39">
@@ -30064,25 +30037,25 @@
     </row>
     <row r="9" spans="1:39">
       <c r="A9" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="O9" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P9" s="21"/>
       <c r="R9" s="179"/>
       <c r="S9" s="179"/>
       <c r="T9" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="U9" s="21"/>
       <c r="Y9" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:39">
       <c r="A10" s="170" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B10" s="170"/>
       <c r="C10" s="170"/>
@@ -30093,7 +30066,7 @@
       <c r="H10" s="170"/>
       <c r="I10" s="170"/>
       <c r="J10" s="170" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K10" s="170"/>
       <c r="L10" s="170"/>
@@ -30120,7 +30093,7 @@
       <c r="AG10" s="170"/>
       <c r="AH10" s="170"/>
       <c r="AI10" s="170" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AJ10" s="170"/>
       <c r="AK10" s="170"/>
@@ -30138,35 +30111,35 @@
       <c r="H11" s="170"/>
       <c r="I11" s="170"/>
       <c r="J11" s="235" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K11" s="236"/>
       <c r="L11" s="236"/>
       <c r="M11" s="236"/>
       <c r="N11" s="236"/>
       <c r="O11" s="235" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P11" s="236"/>
       <c r="Q11" s="236"/>
       <c r="R11" s="236"/>
       <c r="S11" s="236"/>
       <c r="T11" s="235" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U11" s="236"/>
       <c r="V11" s="236"/>
       <c r="W11" s="236"/>
       <c r="X11" s="236"/>
       <c r="Y11" s="235" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z11" s="236"/>
       <c r="AA11" s="236"/>
       <c r="AB11" s="236"/>
       <c r="AC11" s="236"/>
       <c r="AD11" s="235" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AE11" s="236"/>
       <c r="AF11" s="236"/>
@@ -30182,7 +30155,7 @@
       <c r="A12" s="174"/>
       <c r="B12" s="174"/>
       <c r="C12" s="170" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D12" s="170"/>
       <c r="E12" s="170"/>
@@ -30266,7 +30239,7 @@
       <c r="A14" s="174"/>
       <c r="B14" s="174"/>
       <c r="C14" s="170" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D14" s="170"/>
       <c r="E14" s="170"/>
@@ -30350,7 +30323,7 @@
       <c r="A16" s="174"/>
       <c r="B16" s="174"/>
       <c r="C16" s="170" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D16" s="170"/>
       <c r="E16" s="170"/>
@@ -30434,7 +30407,7 @@
       <c r="A18" s="174"/>
       <c r="B18" s="174"/>
       <c r="C18" s="170" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D18" s="170"/>
       <c r="E18" s="170"/>
@@ -30518,7 +30491,7 @@
       <c r="A20" s="174"/>
       <c r="B20" s="174"/>
       <c r="C20" s="170" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D20" s="170"/>
       <c r="E20" s="170"/>
@@ -30602,7 +30575,7 @@
       <c r="A22" s="174"/>
       <c r="B22" s="174"/>
       <c r="C22" s="170" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D22" s="170"/>
       <c r="E22" s="170"/>
@@ -30684,7 +30657,7 @@
     </row>
     <row r="24" spans="1:39" ht="15.6">
       <c r="A24" s="22" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
@@ -30768,7 +30741,7 @@
     </row>
     <row r="26" spans="1:39" ht="12.6" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -30961,9 +30934,7 @@
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
       <c r="Q4" s="24"/>
-      <c r="R4" s="61" t="s">
-        <v>12</v>
-      </c>
+      <c r="R4" s="61"/>
       <c r="S4" s="24"/>
       <c r="T4" s="24"/>
       <c r="U4" s="24"/>
@@ -31007,7 +30978,7 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -31039,7 +31010,7 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
@@ -31071,7 +31042,7 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
@@ -31103,7 +31074,7 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" s="24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
@@ -31165,7 +31136,7 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="24"/>
       <c r="C11" s="24"/>
@@ -31227,13 +31198,13 @@
     </row>
     <row r="13" spans="1:28" ht="13.8" customHeight="1">
       <c r="A13" s="319" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B13" s="320"/>
       <c r="C13" s="320"/>
       <c r="D13" s="323"/>
       <c r="E13" s="162" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="311"/>
       <c r="G13" s="311"/>
@@ -31241,7 +31212,7 @@
       <c r="I13" s="311"/>
       <c r="J13" s="312"/>
       <c r="K13" s="162" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L13" s="311"/>
       <c r="M13" s="311"/>
@@ -31249,7 +31220,7 @@
       <c r="O13" s="311"/>
       <c r="P13" s="312"/>
       <c r="Q13" s="162" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R13" s="311"/>
       <c r="S13" s="311"/>
@@ -31257,7 +31228,7 @@
       <c r="U13" s="311"/>
       <c r="V13" s="312"/>
       <c r="W13" s="162" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X13" s="311"/>
       <c r="Y13" s="311"/>
@@ -31297,7 +31268,7 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="255" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="256"/>
       <c r="C15" s="256"/>
@@ -31329,7 +31300,7 @@
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="255" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="256"/>
       <c r="C16" s="256"/>
@@ -31361,7 +31332,7 @@
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="255" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="256"/>
       <c r="C17" s="256"/>
@@ -31423,13 +31394,13 @@
     </row>
     <row r="19" spans="1:28" ht="13.8" customHeight="1">
       <c r="A19" s="319" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B19" s="320"/>
       <c r="C19" s="320"/>
       <c r="D19" s="323"/>
       <c r="E19" s="162" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19" s="311"/>
       <c r="G19" s="311"/>
@@ -31437,7 +31408,7 @@
       <c r="I19" s="311"/>
       <c r="J19" s="312"/>
       <c r="K19" s="162" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L19" s="311"/>
       <c r="M19" s="311"/>
@@ -31445,7 +31416,7 @@
       <c r="O19" s="311"/>
       <c r="P19" s="312"/>
       <c r="Q19" s="162" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R19" s="311"/>
       <c r="S19" s="311"/>
@@ -31453,7 +31424,7 @@
       <c r="U19" s="311"/>
       <c r="V19" s="312"/>
       <c r="W19" s="162" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X19" s="311"/>
       <c r="Y19" s="311"/>
@@ -31493,7 +31464,7 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="255" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="256"/>
       <c r="C21" s="256"/>
@@ -31525,7 +31496,7 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="255" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="256"/>
       <c r="C22" s="256"/>
@@ -31557,7 +31528,7 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="255" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="256"/>
       <c r="C23" s="256"/>
@@ -31619,13 +31590,13 @@
     </row>
     <row r="25" spans="1:28" ht="13.8" customHeight="1">
       <c r="A25" s="319" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B25" s="320"/>
       <c r="C25" s="320"/>
       <c r="D25" s="323"/>
       <c r="E25" s="162" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" s="311"/>
       <c r="G25" s="311"/>
@@ -31633,7 +31604,7 @@
       <c r="I25" s="311"/>
       <c r="J25" s="312"/>
       <c r="K25" s="162" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L25" s="311"/>
       <c r="M25" s="311"/>
@@ -31641,7 +31612,7 @@
       <c r="O25" s="311"/>
       <c r="P25" s="312"/>
       <c r="Q25" s="162" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R25" s="311"/>
       <c r="S25" s="311"/>
@@ -31649,7 +31620,7 @@
       <c r="U25" s="311"/>
       <c r="V25" s="312"/>
       <c r="W25" s="162" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X25" s="311"/>
       <c r="Y25" s="311"/>
@@ -31689,7 +31660,7 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" s="255" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="256"/>
       <c r="C27" s="256"/>
@@ -31721,7 +31692,7 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="255" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="256"/>
       <c r="C28" s="256"/>
@@ -31753,7 +31724,7 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="255" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="256"/>
       <c r="C29" s="256"/>
@@ -31785,27 +31756,27 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:28">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:28">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -31947,7 +31918,7 @@
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="77"/>
       <c r="C2" s="77"/>
@@ -32069,7 +32040,7 @@
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1">
       <c r="A5" s="78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -32090,7 +32061,7 @@
       <c r="R5" s="165"/>
       <c r="S5" s="165"/>
       <c r="T5" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
@@ -32107,7 +32078,7 @@
       <c r="AG5" s="165"/>
       <c r="AH5" s="165"/>
       <c r="AI5" s="78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
@@ -32153,7 +32124,7 @@
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -32235,7 +32206,7 @@
     </row>
     <row r="9" spans="1:38" ht="13.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -32317,7 +32288,7 @@
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -32359,7 +32330,7 @@
     </row>
     <row r="12" spans="1:38">
       <c r="A12" s="79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="79"/>
       <c r="C12" s="79"/>
@@ -32372,7 +32343,7 @@
       <c r="J12" s="167"/>
       <c r="K12" s="168"/>
       <c r="L12" s="169" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M12" s="170"/>
       <c r="N12" s="170"/>
@@ -32383,7 +32354,7 @@
       <c r="S12" s="170"/>
       <c r="T12" s="170"/>
       <c r="U12" s="170" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V12" s="170"/>
       <c r="W12" s="170"/>
@@ -32394,7 +32365,7 @@
       <c r="AB12" s="170"/>
       <c r="AC12" s="170"/>
       <c r="AD12" s="170" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE12" s="170"/>
       <c r="AF12" s="170"/>
@@ -32407,7 +32378,7 @@
     </row>
     <row r="13" spans="1:38">
       <c r="A13" s="171" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="171"/>
       <c r="C13" s="171"/>
@@ -32449,7 +32420,7 @@
     </row>
     <row r="14" spans="1:38">
       <c r="A14" s="171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="171"/>
       <c r="C14" s="171"/>
@@ -32491,7 +32462,7 @@
     </row>
     <row r="15" spans="1:38">
       <c r="A15" s="171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="171"/>
       <c r="C15" s="171"/>
@@ -32533,7 +32504,7 @@
     </row>
     <row r="16" spans="1:38">
       <c r="A16" s="171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="171"/>
       <c r="C16" s="171"/>
@@ -32575,7 +32546,7 @@
     </row>
     <row r="18" spans="1:38">
       <c r="A18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -32617,7 +32588,7 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" s="79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="79"/>
       <c r="C19" s="79"/>
@@ -32630,7 +32601,7 @@
       <c r="J19" s="167"/>
       <c r="K19" s="168"/>
       <c r="L19" s="169" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M19" s="170"/>
       <c r="N19" s="170"/>
@@ -32641,7 +32612,7 @@
       <c r="S19" s="170"/>
       <c r="T19" s="170"/>
       <c r="U19" s="170" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V19" s="170"/>
       <c r="W19" s="170"/>
@@ -32652,7 +32623,7 @@
       <c r="AB19" s="170"/>
       <c r="AC19" s="170"/>
       <c r="AD19" s="170" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE19" s="170"/>
       <c r="AF19" s="170"/>
@@ -32665,7 +32636,7 @@
     </row>
     <row r="20" spans="1:38">
       <c r="A20" s="171" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="171"/>
       <c r="C20" s="171"/>
@@ -32707,7 +32678,7 @@
     </row>
     <row r="21" spans="1:38">
       <c r="A21" s="171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="171"/>
       <c r="C21" s="171"/>
@@ -32749,7 +32720,7 @@
     </row>
     <row r="22" spans="1:38">
       <c r="A22" s="171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="171"/>
       <c r="C22" s="171"/>
@@ -32791,7 +32762,7 @@
     </row>
     <row r="23" spans="1:38">
       <c r="A23" s="171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="171"/>
       <c r="C23" s="171"/>
@@ -32833,7 +32804,7 @@
     </row>
     <row r="25" spans="1:38">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -32875,7 +32846,7 @@
     </row>
     <row r="26" spans="1:38">
       <c r="A26" s="79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="79"/>
       <c r="C26" s="79"/>
@@ -32888,7 +32859,7 @@
       <c r="J26" s="167"/>
       <c r="K26" s="168"/>
       <c r="L26" s="169" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M26" s="170"/>
       <c r="N26" s="170"/>
@@ -32899,7 +32870,7 @@
       <c r="S26" s="170"/>
       <c r="T26" s="170"/>
       <c r="U26" s="170" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V26" s="170"/>
       <c r="W26" s="170"/>
@@ -32910,7 +32881,7 @@
       <c r="AB26" s="170"/>
       <c r="AC26" s="170"/>
       <c r="AD26" s="170" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE26" s="170"/>
       <c r="AF26" s="170"/>
@@ -32923,7 +32894,7 @@
     </row>
     <row r="27" spans="1:38">
       <c r="A27" s="171" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="171"/>
       <c r="C27" s="171"/>
@@ -32965,7 +32936,7 @@
     </row>
     <row r="28" spans="1:38">
       <c r="A28" s="171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="171"/>
       <c r="C28" s="171"/>
@@ -33007,7 +32978,7 @@
     </row>
     <row r="29" spans="1:38">
       <c r="A29" s="171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="171"/>
       <c r="C29" s="171"/>
@@ -33049,7 +33020,7 @@
     </row>
     <row r="30" spans="1:38">
       <c r="A30" s="171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="171"/>
       <c r="C30" s="171"/>
@@ -33091,7 +33062,7 @@
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -33133,7 +33104,7 @@
     </row>
     <row r="33" spans="1:38">
       <c r="A33" s="79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" s="79"/>
       <c r="C33" s="79"/>
@@ -33146,7 +33117,7 @@
       <c r="J33" s="167"/>
       <c r="K33" s="168"/>
       <c r="L33" s="169" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M33" s="170"/>
       <c r="N33" s="170"/>
@@ -33157,7 +33128,7 @@
       <c r="S33" s="170"/>
       <c r="T33" s="170"/>
       <c r="U33" s="170" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V33" s="170"/>
       <c r="W33" s="170"/>
@@ -33168,7 +33139,7 @@
       <c r="AB33" s="170"/>
       <c r="AC33" s="170"/>
       <c r="AD33" s="170" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE33" s="170"/>
       <c r="AF33" s="170"/>
@@ -33181,7 +33152,7 @@
     </row>
     <row r="34" spans="1:38">
       <c r="A34" s="171" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="171"/>
       <c r="C34" s="171"/>
@@ -33223,7 +33194,7 @@
     </row>
     <row r="35" spans="1:38">
       <c r="A35" s="171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="171"/>
       <c r="C35" s="171"/>
@@ -33265,7 +33236,7 @@
     </row>
     <row r="36" spans="1:38">
       <c r="A36" s="171" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="171"/>
       <c r="C36" s="171"/>
@@ -33307,7 +33278,7 @@
     </row>
     <row r="37" spans="1:38">
       <c r="A37" s="171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="171"/>
       <c r="C37" s="171"/>
@@ -33459,9 +33430,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AP33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="7" width="2.33203125" style="1" customWidth="1"/>
@@ -33513,7 +33483,882 @@
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="23"/>
+    </row>
+    <row r="3" spans="1:39" ht="15" customHeight="1">
+      <c r="A3" s="164"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
+      <c r="L3" s="164"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="164"/>
+      <c r="O3" s="164"/>
+      <c r="P3" s="164"/>
+      <c r="Q3" s="164"/>
+      <c r="R3" s="164"/>
+      <c r="S3" s="164"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="163"/>
+      <c r="AE3" s="163"/>
+      <c r="AF3" s="163"/>
+      <c r="AG3" s="163"/>
+      <c r="AH3" s="163"/>
+      <c r="AI3" s="163"/>
+      <c r="AJ3" s="163"/>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="23"/>
+    </row>
+    <row r="4" spans="1:39" ht="15" customHeight="1">
+      <c r="A4" s="84" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="85"/>
+      <c r="AB4" s="85"/>
+      <c r="AC4" s="85"/>
+      <c r="AD4" s="85"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
+      <c r="AH4" s="85"/>
+      <c r="AI4" s="85"/>
+      <c r="AJ4" s="85"/>
+      <c r="AK4" s="85"/>
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="85"/>
+    </row>
+    <row r="5" spans="1:39" ht="15" customHeight="1">
+      <c r="A5" s="84" t="s">
+        <v>304</v>
+      </c>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="85"/>
+      <c r="AD5" s="85"/>
+      <c r="AE5" s="85"/>
+      <c r="AF5" s="85"/>
+      <c r="AG5" s="85"/>
+      <c r="AH5" s="85"/>
+      <c r="AI5" s="85"/>
+      <c r="AJ5" s="85"/>
+      <c r="AK5" s="85"/>
+      <c r="AL5" s="85"/>
+      <c r="AM5" s="85"/>
+    </row>
+    <row r="6" spans="1:39" ht="15" customHeight="1">
+      <c r="A6" s="84" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" ht="15" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" ht="15" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" ht="15" customHeight="1"/>
+    <row r="10" spans="1:39" ht="15" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" ht="15" customHeight="1">
+      <c r="A11" s="181" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="181"/>
+      <c r="C11" s="181"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="170" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="170"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="170"/>
+      <c r="I11" s="170"/>
+      <c r="J11" s="170"/>
+      <c r="K11" s="170"/>
+      <c r="L11" s="170" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="170"/>
+      <c r="N11" s="170"/>
+      <c r="O11" s="170"/>
+      <c r="P11" s="170"/>
+      <c r="Q11" s="170"/>
+      <c r="R11" s="170"/>
+      <c r="S11" s="170" t="s">
+        <v>67</v>
+      </c>
+      <c r="T11" s="170"/>
+      <c r="U11" s="170"/>
+      <c r="V11" s="170"/>
+      <c r="W11" s="170"/>
+      <c r="X11" s="170"/>
+      <c r="Y11" s="170"/>
+      <c r="Z11" s="170" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA11" s="170"/>
+      <c r="AB11" s="170"/>
+      <c r="AC11" s="170"/>
+      <c r="AD11" s="170"/>
+      <c r="AE11" s="170"/>
+      <c r="AF11" s="170"/>
+      <c r="AG11" s="170" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH11" s="170"/>
+      <c r="AI11" s="170"/>
+      <c r="AJ11" s="170"/>
+      <c r="AK11" s="170"/>
+      <c r="AL11" s="170"/>
+      <c r="AM11" s="170"/>
+    </row>
+    <row r="12" spans="1:39" ht="15" customHeight="1">
+      <c r="A12" s="181"/>
+      <c r="B12" s="181"/>
+      <c r="C12" s="181"/>
+      <c r="D12" s="181"/>
+      <c r="E12" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="170"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="170"/>
+      <c r="J12" s="170"/>
+      <c r="K12" s="170"/>
+      <c r="L12" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="M12" s="170"/>
+      <c r="N12" s="170"/>
+      <c r="O12" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="170"/>
+      <c r="Q12" s="170"/>
+      <c r="R12" s="170"/>
+      <c r="S12" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="T12" s="170"/>
+      <c r="U12" s="170"/>
+      <c r="V12" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="W12" s="170"/>
+      <c r="X12" s="170"/>
+      <c r="Y12" s="170"/>
+      <c r="Z12" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA12" s="170"/>
+      <c r="AB12" s="170"/>
+      <c r="AC12" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD12" s="170"/>
+      <c r="AE12" s="170"/>
+      <c r="AF12" s="170"/>
+      <c r="AG12" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH12" s="170"/>
+      <c r="AI12" s="170"/>
+      <c r="AJ12" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK12" s="170"/>
+      <c r="AL12" s="170"/>
+      <c r="AM12" s="170"/>
+    </row>
+    <row r="13" spans="1:39" ht="15" customHeight="1">
+      <c r="A13" s="185" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="185"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="184"/>
+      <c r="H13" s="182"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="183"/>
+      <c r="K13" s="184"/>
+      <c r="L13" s="182"/>
+      <c r="M13" s="183"/>
+      <c r="N13" s="184"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="183"/>
+      <c r="Q13" s="183"/>
+      <c r="R13" s="184"/>
+      <c r="S13" s="182"/>
+      <c r="T13" s="183"/>
+      <c r="U13" s="184"/>
+      <c r="V13" s="182"/>
+      <c r="W13" s="183"/>
+      <c r="X13" s="183"/>
+      <c r="Y13" s="184"/>
+      <c r="Z13" s="182"/>
+      <c r="AA13" s="183"/>
+      <c r="AB13" s="184"/>
+      <c r="AC13" s="182"/>
+      <c r="AD13" s="183"/>
+      <c r="AE13" s="183"/>
+      <c r="AF13" s="184"/>
+      <c r="AG13" s="182"/>
+      <c r="AH13" s="183"/>
+      <c r="AI13" s="184"/>
+      <c r="AJ13" s="182"/>
+      <c r="AK13" s="183"/>
+      <c r="AL13" s="183"/>
+      <c r="AM13" s="184"/>
+    </row>
+    <row r="14" spans="1:39">
+      <c r="A14" s="185" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="182"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="184"/>
+      <c r="H14" s="182"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="183"/>
+      <c r="K14" s="184"/>
+      <c r="L14" s="182"/>
+      <c r="M14" s="183"/>
+      <c r="N14" s="184"/>
+      <c r="O14" s="182"/>
+      <c r="P14" s="183"/>
+      <c r="Q14" s="183"/>
+      <c r="R14" s="184"/>
+      <c r="S14" s="182"/>
+      <c r="T14" s="183"/>
+      <c r="U14" s="184"/>
+      <c r="V14" s="182"/>
+      <c r="W14" s="183"/>
+      <c r="X14" s="183"/>
+      <c r="Y14" s="184"/>
+      <c r="Z14" s="182"/>
+      <c r="AA14" s="183"/>
+      <c r="AB14" s="184"/>
+      <c r="AC14" s="182"/>
+      <c r="AD14" s="183"/>
+      <c r="AE14" s="183"/>
+      <c r="AF14" s="184"/>
+      <c r="AG14" s="182"/>
+      <c r="AH14" s="183"/>
+      <c r="AI14" s="184"/>
+      <c r="AJ14" s="182"/>
+      <c r="AK14" s="183"/>
+      <c r="AL14" s="183"/>
+      <c r="AM14" s="184"/>
+    </row>
+    <row r="15" spans="1:39">
+      <c r="A15" s="181" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="181"/>
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="170" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="170"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="170"/>
+      <c r="I15" s="170"/>
+      <c r="J15" s="170"/>
+      <c r="K15" s="170"/>
+      <c r="L15" s="170" t="s">
+        <v>75</v>
+      </c>
+      <c r="M15" s="170"/>
+      <c r="N15" s="170"/>
+      <c r="O15" s="170"/>
+      <c r="P15" s="170"/>
+      <c r="Q15" s="170"/>
+      <c r="R15" s="170"/>
+      <c r="S15" s="170" t="s">
+        <v>76</v>
+      </c>
+      <c r="T15" s="170"/>
+      <c r="U15" s="170"/>
+      <c r="V15" s="170"/>
+      <c r="W15" s="170"/>
+      <c r="X15" s="170"/>
+      <c r="Y15" s="170"/>
+      <c r="Z15" s="170" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA15" s="170"/>
+      <c r="AB15" s="170"/>
+      <c r="AC15" s="170"/>
+      <c r="AD15" s="170"/>
+      <c r="AE15" s="170"/>
+      <c r="AF15" s="170"/>
+      <c r="AG15" s="170" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH15" s="170"/>
+      <c r="AI15" s="170"/>
+      <c r="AJ15" s="170"/>
+      <c r="AK15" s="170"/>
+      <c r="AL15" s="170"/>
+      <c r="AM15" s="170"/>
+    </row>
+    <row r="16" spans="1:39">
+      <c r="A16" s="181"/>
+      <c r="B16" s="181"/>
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="170"/>
+      <c r="G16" s="170"/>
+      <c r="H16" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" s="170"/>
+      <c r="J16" s="170"/>
+      <c r="K16" s="170"/>
+      <c r="L16" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" s="170"/>
+      <c r="N16" s="170"/>
+      <c r="O16" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="P16" s="170"/>
+      <c r="Q16" s="170"/>
+      <c r="R16" s="170"/>
+      <c r="S16" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="T16" s="170"/>
+      <c r="U16" s="170"/>
+      <c r="V16" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="W16" s="170"/>
+      <c r="X16" s="170"/>
+      <c r="Y16" s="170"/>
+      <c r="Z16" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA16" s="170"/>
+      <c r="AB16" s="170"/>
+      <c r="AC16" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD16" s="170"/>
+      <c r="AE16" s="170"/>
+      <c r="AF16" s="170"/>
+      <c r="AG16" s="170" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH16" s="170"/>
+      <c r="AI16" s="170"/>
+      <c r="AJ16" s="170" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK16" s="170"/>
+      <c r="AL16" s="170"/>
+      <c r="AM16" s="170"/>
+    </row>
+    <row r="17" spans="1:39">
+      <c r="A17" s="185" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="182"/>
+      <c r="F17" s="183"/>
+      <c r="G17" s="184"/>
+      <c r="H17" s="182"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="183"/>
+      <c r="K17" s="184"/>
+      <c r="L17" s="182"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="184"/>
+      <c r="O17" s="182"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="183"/>
+      <c r="R17" s="184"/>
+      <c r="S17" s="182"/>
+      <c r="T17" s="183"/>
+      <c r="U17" s="184"/>
+      <c r="V17" s="182"/>
+      <c r="W17" s="183"/>
+      <c r="X17" s="183"/>
+      <c r="Y17" s="184"/>
+      <c r="Z17" s="182"/>
+      <c r="AA17" s="183"/>
+      <c r="AB17" s="184"/>
+      <c r="AC17" s="182"/>
+      <c r="AD17" s="183"/>
+      <c r="AE17" s="183"/>
+      <c r="AF17" s="184"/>
+      <c r="AG17" s="182"/>
+      <c r="AH17" s="183"/>
+      <c r="AI17" s="184"/>
+      <c r="AJ17" s="182"/>
+      <c r="AK17" s="183"/>
+      <c r="AL17" s="183"/>
+      <c r="AM17" s="184"/>
+    </row>
+    <row r="18" spans="1:39">
+      <c r="A18" s="185" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="182"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="184"/>
+      <c r="H18" s="182"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="183"/>
+      <c r="K18" s="184"/>
+      <c r="L18" s="182"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="184"/>
+      <c r="O18" s="182"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="183"/>
+      <c r="R18" s="184"/>
+      <c r="S18" s="182"/>
+      <c r="T18" s="183"/>
+      <c r="U18" s="184"/>
+      <c r="V18" s="182"/>
+      <c r="W18" s="183"/>
+      <c r="X18" s="183"/>
+      <c r="Y18" s="184"/>
+      <c r="Z18" s="182"/>
+      <c r="AA18" s="183"/>
+      <c r="AB18" s="184"/>
+      <c r="AC18" s="182"/>
+      <c r="AD18" s="183"/>
+      <c r="AE18" s="183"/>
+      <c r="AF18" s="184"/>
+      <c r="AG18" s="182"/>
+      <c r="AH18" s="183"/>
+      <c r="AI18" s="184"/>
+      <c r="AJ18" s="182"/>
+      <c r="AK18" s="183"/>
+      <c r="AL18" s="183"/>
+      <c r="AM18" s="184"/>
+    </row>
+    <row r="19" spans="1:39">
+      <c r="A19" s="107" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="107"/>
+      <c r="M19" s="107"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="107"/>
+      <c r="P19" s="107"/>
+      <c r="Q19" s="107"/>
+      <c r="R19" s="107"/>
+      <c r="S19" s="107"/>
+      <c r="T19" s="107"/>
+      <c r="U19" s="107"/>
+      <c r="V19" s="107"/>
+      <c r="W19" s="107"/>
+      <c r="X19" s="107"/>
+      <c r="Y19" s="107"/>
+      <c r="Z19" s="107"/>
+      <c r="AA19" s="107"/>
+      <c r="AB19" s="107"/>
+      <c r="AC19" s="107"/>
+      <c r="AD19" s="107"/>
+      <c r="AE19" s="107"/>
+      <c r="AF19" s="107"/>
+      <c r="AG19" s="107"/>
+      <c r="AH19" s="107"/>
+      <c r="AI19" s="107"/>
+      <c r="AJ19" s="107"/>
+      <c r="AK19" s="107"/>
+      <c r="AL19" s="107"/>
+      <c r="AM19" s="107"/>
+    </row>
+    <row r="20" spans="1:39">
+      <c r="A20" s="107" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="107"/>
+      <c r="Q20" s="107"/>
+      <c r="R20" s="107"/>
+      <c r="S20" s="107"/>
+      <c r="T20" s="107"/>
+      <c r="U20" s="107"/>
+      <c r="V20" s="107"/>
+      <c r="W20" s="107"/>
+      <c r="X20" s="107"/>
+      <c r="Y20" s="107"/>
+      <c r="Z20" s="107"/>
+      <c r="AA20" s="107"/>
+      <c r="AB20" s="107"/>
+      <c r="AC20" s="107"/>
+      <c r="AD20" s="107"/>
+      <c r="AE20" s="107"/>
+      <c r="AF20" s="107"/>
+      <c r="AG20" s="107"/>
+      <c r="AH20" s="107"/>
+      <c r="AI20" s="107"/>
+      <c r="AJ20" s="107"/>
+      <c r="AK20" s="107"/>
+      <c r="AL20" s="107"/>
+      <c r="AM20" s="107"/>
+    </row>
+    <row r="21" spans="1:39">
+      <c r="A21" s="107" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="107"/>
+      <c r="O21" s="107"/>
+      <c r="P21" s="107"/>
+      <c r="Q21" s="107"/>
+      <c r="R21" s="107"/>
+      <c r="S21" s="107"/>
+      <c r="T21" s="107"/>
+      <c r="U21" s="107"/>
+      <c r="V21" s="107"/>
+      <c r="W21" s="107"/>
+      <c r="X21" s="107"/>
+      <c r="Y21" s="107"/>
+      <c r="Z21" s="107"/>
+      <c r="AA21" s="107"/>
+      <c r="AB21" s="107"/>
+      <c r="AC21" s="107"/>
+      <c r="AD21" s="107"/>
+      <c r="AE21" s="107"/>
+      <c r="AF21" s="107"/>
+      <c r="AG21" s="107"/>
+      <c r="AH21" s="107"/>
+      <c r="AI21" s="107"/>
+      <c r="AJ21" s="107"/>
+      <c r="AK21" s="107"/>
+      <c r="AL21" s="107"/>
+      <c r="AM21" s="107"/>
+    </row>
+    <row r="22" spans="1:39">
+      <c r="A22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39">
+      <c r="AM23" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="79">
+    <mergeCell ref="AD3:AJ3"/>
+    <mergeCell ref="A15:D16"/>
+    <mergeCell ref="AJ17:AM17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="S18:U18"/>
+    <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="Z18:AB18"/>
+    <mergeCell ref="AC18:AF18"/>
+    <mergeCell ref="AG18:AI18"/>
+    <mergeCell ref="AJ18:AM18"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="Z17:AB17"/>
+    <mergeCell ref="AC17:AF17"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AJ16:AM16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="S16:U16"/>
+    <mergeCell ref="E15:K15"/>
+    <mergeCell ref="L15:R15"/>
+    <mergeCell ref="S15:Y15"/>
+    <mergeCell ref="Z15:AF15"/>
+    <mergeCell ref="AG15:AM15"/>
+    <mergeCell ref="AJ14:AM14"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="V13:Y13"/>
+    <mergeCell ref="Z13:AB13"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="S14:U14"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="AJ12:AM12"/>
+    <mergeCell ref="AG13:AI13"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="AJ13:AM13"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="E11:K11"/>
+    <mergeCell ref="L11:R11"/>
+    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="Z11:AF11"/>
+    <mergeCell ref="AG11:AM11"/>
+    <mergeCell ref="A11:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="V12:Y12"/>
+    <mergeCell ref="Z12:AB12"/>
+    <mergeCell ref="AC12:AF12"/>
+  </mergeCells>
+  <phoneticPr fontId="41" type="noConversion"/>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L
+Form Code表格编号: NGB_SFL_F_7.8_Primark-PHY_0005_CS_A.0&amp;R&amp;G</oddHeader>
+    <oddFooter>&amp;L测试/日期Conducted by/Date:
+&amp;U                                                   &amp;U.&amp;C复核/日期Checked by/Date:
+&amp;U                                            &amp;U.&amp;R测试环境Test Condition:
+&amp;U                &amp;U ℃,&amp;U                 &amp;U%RH</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:AP33"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2" style="1" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" style="1" customWidth="1"/>
+    <col min="32" max="39" width="2.33203125" style="1" customWidth="1"/>
+    <col min="40" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" ht="15" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="163"/>
+      <c r="N1" s="163"/>
+      <c r="O1" s="163"/>
+      <c r="P1" s="163"/>
+      <c r="Q1" s="163"/>
+      <c r="R1" s="163"/>
+      <c r="S1" s="163"/>
+      <c r="T1" s="163"/>
+      <c r="U1" s="163"/>
+      <c r="V1" s="163"/>
+      <c r="W1" s="163"/>
+      <c r="X1" s="163"/>
+      <c r="Y1" s="163"/>
+      <c r="Z1" s="163"/>
+      <c r="AA1" s="163"/>
+      <c r="AB1" s="163"/>
+      <c r="AC1" s="163"/>
+      <c r="AD1" s="163"/>
+      <c r="AE1" s="163"/>
+      <c r="AF1" s="163"/>
+      <c r="AG1" s="163"/>
+      <c r="AH1" s="163"/>
+      <c r="AI1" s="163"/>
+      <c r="AJ1" s="163"/>
+      <c r="AK1" s="163"/>
+      <c r="AL1" s="163"/>
+      <c r="AM1" s="23"/>
+    </row>
+    <row r="2" spans="1:39" ht="15" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -33635,7 +34480,7 @@
     </row>
     <row r="5" spans="1:39" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="166"/>
       <c r="F5" s="166"/>
@@ -33713,7 +34558,7 @@
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -33808,35 +34653,35 @@
       <c r="G9" s="179"/>
       <c r="H9" s="180"/>
       <c r="I9" s="173" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J9" s="173"/>
       <c r="K9" s="173"/>
       <c r="L9" s="173"/>
       <c r="M9" s="173"/>
       <c r="N9" s="173" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O9" s="173"/>
       <c r="P9" s="173"/>
       <c r="Q9" s="173"/>
       <c r="R9" s="173"/>
       <c r="S9" s="173" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T9" s="173"/>
       <c r="U9" s="173"/>
       <c r="V9" s="173"/>
       <c r="W9" s="173"/>
       <c r="X9" s="173" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y9" s="173"/>
       <c r="Z9" s="173"/>
       <c r="AA9" s="173"/>
       <c r="AB9" s="173"/>
       <c r="AC9" s="173" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AD9" s="173"/>
       <c r="AE9" s="173"/>
@@ -34138,7 +34983,7 @@
     </row>
     <row r="17" spans="1:42">
       <c r="A17" s="3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -34233,35 +35078,35 @@
       <c r="G19" s="179"/>
       <c r="H19" s="180"/>
       <c r="I19" s="173" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J19" s="173"/>
       <c r="K19" s="173"/>
       <c r="L19" s="173"/>
       <c r="M19" s="173"/>
       <c r="N19" s="173" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O19" s="173"/>
       <c r="P19" s="173"/>
       <c r="Q19" s="173"/>
       <c r="R19" s="173"/>
       <c r="S19" s="173" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T19" s="173"/>
       <c r="U19" s="173"/>
       <c r="V19" s="173"/>
       <c r="W19" s="173"/>
       <c r="X19" s="173" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y19" s="173"/>
       <c r="Z19" s="173"/>
       <c r="AA19" s="173"/>
       <c r="AB19" s="173"/>
       <c r="AC19" s="173" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AD19" s="173"/>
       <c r="AE19" s="173"/>
@@ -34561,12 +35406,12 @@
     </row>
     <row r="27" spans="1:42">
       <c r="A27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:42">
       <c r="A28" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:42">
@@ -34592,7 +35437,7 @@
     </row>
     <row r="30" spans="1:42" ht="16.2">
       <c r="A30" s="36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B30" s="36"/>
       <c r="C30" s="36"/>
@@ -34600,13 +35445,13 @@
       <c r="E30" s="136"/>
       <c r="F30" s="136"/>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H30" s="130"/>
       <c r="I30" s="130"/>
       <c r="J30" s="130"/>
       <c r="K30" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L30" s="36"/>
       <c r="M30" s="36"/>
@@ -34620,7 +35465,7 @@
       <c r="U30" s="130"/>
       <c r="V30" s="130"/>
       <c r="W30" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="X30" s="36"/>
       <c r="Y30" s="36"/>
@@ -34649,7 +35494,7 @@
       <c r="O31" s="163"/>
       <c r="P31" s="163"/>
       <c r="Q31" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R31" s="130"/>
       <c r="S31" s="130"/>
@@ -34665,7 +35510,7 @@
       <c r="AC31" s="130"/>
       <c r="AD31" s="130"/>
       <c r="AE31" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AF31" s="130"/>
       <c r="AG31" s="130"/>
@@ -34674,7 +35519,7 @@
       <c r="AJ31" s="130"/>
       <c r="AK31" s="130"/>
       <c r="AL31" s="119" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AM31" s="36"/>
       <c r="AN31" s="36"/>
@@ -34724,7 +35569,7 @@
     </row>
     <row r="33" spans="1:31" ht="16.2">
       <c r="A33" s="74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" s="36"/>
       <c r="C33" s="36"/>
@@ -34735,7 +35580,7 @@
       <c r="H33" s="130"/>
       <c r="I33" s="130"/>
       <c r="J33" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K33" s="36"/>
       <c r="L33" s="130"/>
@@ -34890,9 +35735,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AM23"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="Sheet14"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="7" width="2.33203125" style="1" customWidth="1"/>
@@ -34944,884 +35790,7 @@
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6"/>
-      <c r="AL2" s="6"/>
-      <c r="AM2" s="23"/>
-    </row>
-    <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="164"/>
-      <c r="P3" s="164"/>
-      <c r="Q3" s="164"/>
-      <c r="R3" s="164"/>
-      <c r="S3" s="164"/>
-      <c r="T3" s="164"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="163"/>
-      <c r="AE3" s="163"/>
-      <c r="AF3" s="163"/>
-      <c r="AG3" s="163"/>
-      <c r="AH3" s="163"/>
-      <c r="AI3" s="163"/>
-      <c r="AJ3" s="163"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="23"/>
-    </row>
-    <row r="4" spans="1:39" ht="15" customHeight="1">
-      <c r="A4" s="84" t="s">
-        <v>307</v>
-      </c>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="85"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="85"/>
-      <c r="W4" s="85"/>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="85"/>
-      <c r="Z4" s="85"/>
-      <c r="AA4" s="85"/>
-      <c r="AB4" s="85"/>
-      <c r="AC4" s="85"/>
-      <c r="AD4" s="85"/>
-      <c r="AE4" s="85"/>
-      <c r="AF4" s="85"/>
-      <c r="AG4" s="85"/>
-      <c r="AH4" s="85"/>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="85"/>
-      <c r="AK4" s="85"/>
-      <c r="AL4" s="85"/>
-      <c r="AM4" s="85"/>
-    </row>
-    <row r="5" spans="1:39" ht="15" customHeight="1">
-      <c r="A5" s="84" t="s">
-        <v>306</v>
-      </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="85"/>
-      <c r="V5" s="85"/>
-      <c r="W5" s="85"/>
-      <c r="X5" s="85"/>
-      <c r="Y5" s="85"/>
-      <c r="Z5" s="85"/>
-      <c r="AA5" s="85"/>
-      <c r="AB5" s="85"/>
-      <c r="AC5" s="85"/>
-      <c r="AD5" s="85"/>
-      <c r="AE5" s="85"/>
-      <c r="AF5" s="85"/>
-      <c r="AG5" s="85"/>
-      <c r="AH5" s="85"/>
-      <c r="AI5" s="85"/>
-      <c r="AJ5" s="85"/>
-      <c r="AK5" s="85"/>
-      <c r="AL5" s="85"/>
-      <c r="AM5" s="85"/>
-    </row>
-    <row r="6" spans="1:39" ht="15" customHeight="1">
-      <c r="A6" s="84" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="7" spans="1:39" ht="15" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:39" ht="15" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:39" ht="15" customHeight="1"/>
-    <row r="10" spans="1:39" ht="15" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:39" ht="15" customHeight="1">
-      <c r="A11" s="181" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="170" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="170"/>
-      <c r="G11" s="170"/>
-      <c r="H11" s="170"/>
-      <c r="I11" s="170"/>
-      <c r="J11" s="170"/>
-      <c r="K11" s="170"/>
-      <c r="L11" s="170" t="s">
-        <v>68</v>
-      </c>
-      <c r="M11" s="170"/>
-      <c r="N11" s="170"/>
-      <c r="O11" s="170"/>
-      <c r="P11" s="170"/>
-      <c r="Q11" s="170"/>
-      <c r="R11" s="170"/>
-      <c r="S11" s="170" t="s">
-        <v>69</v>
-      </c>
-      <c r="T11" s="170"/>
-      <c r="U11" s="170"/>
-      <c r="V11" s="170"/>
-      <c r="W11" s="170"/>
-      <c r="X11" s="170"/>
-      <c r="Y11" s="170"/>
-      <c r="Z11" s="170" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA11" s="170"/>
-      <c r="AB11" s="170"/>
-      <c r="AC11" s="170"/>
-      <c r="AD11" s="170"/>
-      <c r="AE11" s="170"/>
-      <c r="AF11" s="170"/>
-      <c r="AG11" s="170" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH11" s="170"/>
-      <c r="AI11" s="170"/>
-      <c r="AJ11" s="170"/>
-      <c r="AK11" s="170"/>
-      <c r="AL11" s="170"/>
-      <c r="AM11" s="170"/>
-    </row>
-    <row r="12" spans="1:39" ht="15" customHeight="1">
-      <c r="A12" s="181"/>
-      <c r="B12" s="181"/>
-      <c r="C12" s="181"/>
-      <c r="D12" s="181"/>
-      <c r="E12" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" s="170"/>
-      <c r="G12" s="170"/>
-      <c r="H12" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" s="170"/>
-      <c r="J12" s="170"/>
-      <c r="K12" s="170"/>
-      <c r="L12" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="M12" s="170"/>
-      <c r="N12" s="170"/>
-      <c r="O12" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="P12" s="170"/>
-      <c r="Q12" s="170"/>
-      <c r="R12" s="170"/>
-      <c r="S12" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="T12" s="170"/>
-      <c r="U12" s="170"/>
-      <c r="V12" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="W12" s="170"/>
-      <c r="X12" s="170"/>
-      <c r="Y12" s="170"/>
-      <c r="Z12" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA12" s="170"/>
-      <c r="AB12" s="170"/>
-      <c r="AC12" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD12" s="170"/>
-      <c r="AE12" s="170"/>
-      <c r="AF12" s="170"/>
-      <c r="AG12" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH12" s="170"/>
-      <c r="AI12" s="170"/>
-      <c r="AJ12" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK12" s="170"/>
-      <c r="AL12" s="170"/>
-      <c r="AM12" s="170"/>
-    </row>
-    <row r="13" spans="1:39" ht="15" customHeight="1">
-      <c r="A13" s="185" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="185"/>
-      <c r="C13" s="185"/>
-      <c r="D13" s="185"/>
-      <c r="E13" s="182"/>
-      <c r="F13" s="183"/>
-      <c r="G13" s="184"/>
-      <c r="H13" s="182"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="183"/>
-      <c r="K13" s="184"/>
-      <c r="L13" s="182"/>
-      <c r="M13" s="183"/>
-      <c r="N13" s="184"/>
-      <c r="O13" s="182"/>
-      <c r="P13" s="183"/>
-      <c r="Q13" s="183"/>
-      <c r="R13" s="184"/>
-      <c r="S13" s="182"/>
-      <c r="T13" s="183"/>
-      <c r="U13" s="184"/>
-      <c r="V13" s="182"/>
-      <c r="W13" s="183"/>
-      <c r="X13" s="183"/>
-      <c r="Y13" s="184"/>
-      <c r="Z13" s="182"/>
-      <c r="AA13" s="183"/>
-      <c r="AB13" s="184"/>
-      <c r="AC13" s="182"/>
-      <c r="AD13" s="183"/>
-      <c r="AE13" s="183"/>
-      <c r="AF13" s="184"/>
-      <c r="AG13" s="182"/>
-      <c r="AH13" s="183"/>
-      <c r="AI13" s="184"/>
-      <c r="AJ13" s="182"/>
-      <c r="AK13" s="183"/>
-      <c r="AL13" s="183"/>
-      <c r="AM13" s="184"/>
-    </row>
-    <row r="14" spans="1:39">
-      <c r="A14" s="185" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
-      <c r="E14" s="182"/>
-      <c r="F14" s="183"/>
-      <c r="G14" s="184"/>
-      <c r="H14" s="182"/>
-      <c r="I14" s="183"/>
-      <c r="J14" s="183"/>
-      <c r="K14" s="184"/>
-      <c r="L14" s="182"/>
-      <c r="M14" s="183"/>
-      <c r="N14" s="184"/>
-      <c r="O14" s="182"/>
-      <c r="P14" s="183"/>
-      <c r="Q14" s="183"/>
-      <c r="R14" s="184"/>
-      <c r="S14" s="182"/>
-      <c r="T14" s="183"/>
-      <c r="U14" s="184"/>
-      <c r="V14" s="182"/>
-      <c r="W14" s="183"/>
-      <c r="X14" s="183"/>
-      <c r="Y14" s="184"/>
-      <c r="Z14" s="182"/>
-      <c r="AA14" s="183"/>
-      <c r="AB14" s="184"/>
-      <c r="AC14" s="182"/>
-      <c r="AD14" s="183"/>
-      <c r="AE14" s="183"/>
-      <c r="AF14" s="184"/>
-      <c r="AG14" s="182"/>
-      <c r="AH14" s="183"/>
-      <c r="AI14" s="184"/>
-      <c r="AJ14" s="182"/>
-      <c r="AK14" s="183"/>
-      <c r="AL14" s="183"/>
-      <c r="AM14" s="184"/>
-    </row>
-    <row r="15" spans="1:39">
-      <c r="A15" s="181" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="181"/>
-      <c r="C15" s="181"/>
-      <c r="D15" s="181"/>
-      <c r="E15" s="170" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="170"/>
-      <c r="G15" s="170"/>
-      <c r="H15" s="170"/>
-      <c r="I15" s="170"/>
-      <c r="J15" s="170"/>
-      <c r="K15" s="170"/>
-      <c r="L15" s="170" t="s">
-        <v>77</v>
-      </c>
-      <c r="M15" s="170"/>
-      <c r="N15" s="170"/>
-      <c r="O15" s="170"/>
-      <c r="P15" s="170"/>
-      <c r="Q15" s="170"/>
-      <c r="R15" s="170"/>
-      <c r="S15" s="170" t="s">
-        <v>78</v>
-      </c>
-      <c r="T15" s="170"/>
-      <c r="U15" s="170"/>
-      <c r="V15" s="170"/>
-      <c r="W15" s="170"/>
-      <c r="X15" s="170"/>
-      <c r="Y15" s="170"/>
-      <c r="Z15" s="170" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA15" s="170"/>
-      <c r="AB15" s="170"/>
-      <c r="AC15" s="170"/>
-      <c r="AD15" s="170"/>
-      <c r="AE15" s="170"/>
-      <c r="AF15" s="170"/>
-      <c r="AG15" s="170" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH15" s="170"/>
-      <c r="AI15" s="170"/>
-      <c r="AJ15" s="170"/>
-      <c r="AK15" s="170"/>
-      <c r="AL15" s="170"/>
-      <c r="AM15" s="170"/>
-    </row>
-    <row r="16" spans="1:39">
-      <c r="A16" s="181"/>
-      <c r="B16" s="181"/>
-      <c r="C16" s="181"/>
-      <c r="D16" s="181"/>
-      <c r="E16" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="170"/>
-      <c r="G16" s="170"/>
-      <c r="H16" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="170"/>
-      <c r="J16" s="170"/>
-      <c r="K16" s="170"/>
-      <c r="L16" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="M16" s="170"/>
-      <c r="N16" s="170"/>
-      <c r="O16" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="P16" s="170"/>
-      <c r="Q16" s="170"/>
-      <c r="R16" s="170"/>
-      <c r="S16" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="T16" s="170"/>
-      <c r="U16" s="170"/>
-      <c r="V16" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="W16" s="170"/>
-      <c r="X16" s="170"/>
-      <c r="Y16" s="170"/>
-      <c r="Z16" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA16" s="170"/>
-      <c r="AB16" s="170"/>
-      <c r="AC16" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD16" s="170"/>
-      <c r="AE16" s="170"/>
-      <c r="AF16" s="170"/>
-      <c r="AG16" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH16" s="170"/>
-      <c r="AI16" s="170"/>
-      <c r="AJ16" s="170" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK16" s="170"/>
-      <c r="AL16" s="170"/>
-      <c r="AM16" s="170"/>
-    </row>
-    <row r="17" spans="1:39">
-      <c r="A17" s="185" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="185"/>
-      <c r="C17" s="185"/>
-      <c r="D17" s="185"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="183"/>
-      <c r="G17" s="184"/>
-      <c r="H17" s="182"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="183"/>
-      <c r="K17" s="184"/>
-      <c r="L17" s="182"/>
-      <c r="M17" s="183"/>
-      <c r="N17" s="184"/>
-      <c r="O17" s="182"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="183"/>
-      <c r="R17" s="184"/>
-      <c r="S17" s="182"/>
-      <c r="T17" s="183"/>
-      <c r="U17" s="184"/>
-      <c r="V17" s="182"/>
-      <c r="W17" s="183"/>
-      <c r="X17" s="183"/>
-      <c r="Y17" s="184"/>
-      <c r="Z17" s="182"/>
-      <c r="AA17" s="183"/>
-      <c r="AB17" s="184"/>
-      <c r="AC17" s="182"/>
-      <c r="AD17" s="183"/>
-      <c r="AE17" s="183"/>
-      <c r="AF17" s="184"/>
-      <c r="AG17" s="182"/>
-      <c r="AH17" s="183"/>
-      <c r="AI17" s="184"/>
-      <c r="AJ17" s="182"/>
-      <c r="AK17" s="183"/>
-      <c r="AL17" s="183"/>
-      <c r="AM17" s="184"/>
-    </row>
-    <row r="18" spans="1:39">
-      <c r="A18" s="185" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="182"/>
-      <c r="F18" s="183"/>
-      <c r="G18" s="184"/>
-      <c r="H18" s="182"/>
-      <c r="I18" s="183"/>
-      <c r="J18" s="183"/>
-      <c r="K18" s="184"/>
-      <c r="L18" s="182"/>
-      <c r="M18" s="183"/>
-      <c r="N18" s="184"/>
-      <c r="O18" s="182"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="183"/>
-      <c r="R18" s="184"/>
-      <c r="S18" s="182"/>
-      <c r="T18" s="183"/>
-      <c r="U18" s="184"/>
-      <c r="V18" s="182"/>
-      <c r="W18" s="183"/>
-      <c r="X18" s="183"/>
-      <c r="Y18" s="184"/>
-      <c r="Z18" s="182"/>
-      <c r="AA18" s="183"/>
-      <c r="AB18" s="184"/>
-      <c r="AC18" s="182"/>
-      <c r="AD18" s="183"/>
-      <c r="AE18" s="183"/>
-      <c r="AF18" s="184"/>
-      <c r="AG18" s="182"/>
-      <c r="AH18" s="183"/>
-      <c r="AI18" s="184"/>
-      <c r="AJ18" s="182"/>
-      <c r="AK18" s="183"/>
-      <c r="AL18" s="183"/>
-      <c r="AM18" s="184"/>
-    </row>
-    <row r="19" spans="1:39">
-      <c r="A19" s="107" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="107"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="107"/>
-      <c r="T19" s="107"/>
-      <c r="U19" s="107"/>
-      <c r="V19" s="107"/>
-      <c r="W19" s="107"/>
-      <c r="X19" s="107"/>
-      <c r="Y19" s="107"/>
-      <c r="Z19" s="107"/>
-      <c r="AA19" s="107"/>
-      <c r="AB19" s="107"/>
-      <c r="AC19" s="107"/>
-      <c r="AD19" s="107"/>
-      <c r="AE19" s="107"/>
-      <c r="AF19" s="107"/>
-      <c r="AG19" s="107"/>
-      <c r="AH19" s="107"/>
-      <c r="AI19" s="107"/>
-      <c r="AJ19" s="107"/>
-      <c r="AK19" s="107"/>
-      <c r="AL19" s="107"/>
-      <c r="AM19" s="107"/>
-    </row>
-    <row r="20" spans="1:39">
-      <c r="A20" s="107" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="107"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107"/>
-      <c r="M20" s="107"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="107"/>
-      <c r="P20" s="107"/>
-      <c r="Q20" s="107"/>
-      <c r="R20" s="107"/>
-      <c r="S20" s="107"/>
-      <c r="T20" s="107"/>
-      <c r="U20" s="107"/>
-      <c r="V20" s="107"/>
-      <c r="W20" s="107"/>
-      <c r="X20" s="107"/>
-      <c r="Y20" s="107"/>
-      <c r="Z20" s="107"/>
-      <c r="AA20" s="107"/>
-      <c r="AB20" s="107"/>
-      <c r="AC20" s="107"/>
-      <c r="AD20" s="107"/>
-      <c r="AE20" s="107"/>
-      <c r="AF20" s="107"/>
-      <c r="AG20" s="107"/>
-      <c r="AH20" s="107"/>
-      <c r="AI20" s="107"/>
-      <c r="AJ20" s="107"/>
-      <c r="AK20" s="107"/>
-      <c r="AL20" s="107"/>
-      <c r="AM20" s="107"/>
-    </row>
-    <row r="21" spans="1:39">
-      <c r="A21" s="107" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="107"/>
-      <c r="N21" s="107"/>
-      <c r="O21" s="107"/>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="107"/>
-      <c r="S21" s="107"/>
-      <c r="T21" s="107"/>
-      <c r="U21" s="107"/>
-      <c r="V21" s="107"/>
-      <c r="W21" s="107"/>
-      <c r="X21" s="107"/>
-      <c r="Y21" s="107"/>
-      <c r="Z21" s="107"/>
-      <c r="AA21" s="107"/>
-      <c r="AB21" s="107"/>
-      <c r="AC21" s="107"/>
-      <c r="AD21" s="107"/>
-      <c r="AE21" s="107"/>
-      <c r="AF21" s="107"/>
-      <c r="AG21" s="107"/>
-      <c r="AH21" s="107"/>
-      <c r="AI21" s="107"/>
-      <c r="AJ21" s="107"/>
-      <c r="AK21" s="107"/>
-      <c r="AL21" s="107"/>
-      <c r="AM21" s="107"/>
-    </row>
-    <row r="22" spans="1:39">
-      <c r="A22" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:39">
-      <c r="AM23" s="73"/>
-    </row>
-  </sheetData>
-  <mergeCells count="79">
-    <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="A15:D16"/>
-    <mergeCell ref="AJ17:AM17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="V18:Y18"/>
-    <mergeCell ref="Z18:AB18"/>
-    <mergeCell ref="AC18:AF18"/>
-    <mergeCell ref="AG18:AI18"/>
-    <mergeCell ref="AJ18:AM18"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="Z17:AB17"/>
-    <mergeCell ref="AC17:AF17"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="V16:Y16"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="AG16:AI16"/>
-    <mergeCell ref="AJ16:AM16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="S16:U16"/>
-    <mergeCell ref="E15:K15"/>
-    <mergeCell ref="L15:R15"/>
-    <mergeCell ref="S15:Y15"/>
-    <mergeCell ref="Z15:AF15"/>
-    <mergeCell ref="AG15:AM15"/>
-    <mergeCell ref="AJ14:AM14"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="V13:Y13"/>
-    <mergeCell ref="Z13:AB13"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="S14:U14"/>
-    <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="AJ12:AM12"/>
-    <mergeCell ref="AG13:AI13"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="AJ13:AM13"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="E11:K11"/>
-    <mergeCell ref="L11:R11"/>
-    <mergeCell ref="S11:Y11"/>
-    <mergeCell ref="Z11:AF11"/>
-    <mergeCell ref="AG11:AM11"/>
-    <mergeCell ref="A11:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="V12:Y12"/>
-    <mergeCell ref="Z12:AB12"/>
-    <mergeCell ref="AC12:AF12"/>
-  </mergeCells>
-  <phoneticPr fontId="41" type="noConversion"/>
-  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="98" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;L
-Form Code表格编号: NGB_SFL_F_7.8_Primark-PHY_0005_CS_A.0&amp;R&amp;G</oddHeader>
-    <oddFooter>&amp;L测试/日期Conducted by/Date:
-&amp;U                                                   &amp;U.&amp;C复核/日期Checked by/Date:
-&amp;U                                            &amp;U.&amp;R测试环境Test Condition:
-&amp;U                &amp;U ℃,&amp;U                 &amp;U%RH</oddFooter>
-  </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:AM39"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="7" width="2.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="2" style="1" customWidth="1"/>
-    <col min="9" max="31" width="2.109375" style="1" customWidth="1"/>
-    <col min="32" max="39" width="2.33203125" style="1" customWidth="1"/>
-    <col min="40" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:39" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="163"/>
-      <c r="N1" s="163"/>
-      <c r="O1" s="163"/>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="163"/>
-      <c r="S1" s="163"/>
-      <c r="T1" s="163"/>
-      <c r="U1" s="163"/>
-      <c r="V1" s="163"/>
-      <c r="W1" s="163"/>
-      <c r="X1" s="163"/>
-      <c r="Y1" s="163"/>
-      <c r="Z1" s="163"/>
-      <c r="AA1" s="163"/>
-      <c r="AB1" s="163"/>
-      <c r="AC1" s="163"/>
-      <c r="AD1" s="163"/>
-      <c r="AE1" s="163"/>
-      <c r="AF1" s="163"/>
-      <c r="AG1" s="163"/>
-      <c r="AH1" s="163"/>
-      <c r="AI1" s="163"/>
-      <c r="AJ1" s="163"/>
-      <c r="AK1" s="163"/>
-      <c r="AL1" s="163"/>
-      <c r="AM1" s="23"/>
-    </row>
-    <row r="2" spans="1:39" ht="15" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -35885,7 +35854,7 @@
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Z3" s="7"/>
       <c r="AA3" s="17"/>
@@ -35904,7 +35873,7 @@
     </row>
     <row r="4" spans="1:39" ht="15" customHeight="1">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -35947,13 +35916,13 @@
     </row>
     <row r="5" spans="1:39" ht="15" customHeight="1">
       <c r="A5" s="185" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B5" s="185"/>
       <c r="C5" s="185"/>
       <c r="D5" s="185"/>
       <c r="E5" s="173" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F5" s="173"/>
       <c r="G5" s="173"/>
@@ -35962,7 +35931,7 @@
       <c r="J5" s="173"/>
       <c r="K5" s="173"/>
       <c r="L5" s="173" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M5" s="173"/>
       <c r="N5" s="173"/>
@@ -35971,7 +35940,7 @@
       <c r="Q5" s="173"/>
       <c r="R5" s="173"/>
       <c r="S5" s="173" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="T5" s="173"/>
       <c r="U5" s="173"/>
@@ -35980,7 +35949,7 @@
       <c r="X5" s="173"/>
       <c r="Y5" s="173"/>
       <c r="Z5" s="173" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AA5" s="173"/>
       <c r="AB5" s="173"/>
@@ -35989,7 +35958,7 @@
       <c r="AE5" s="173"/>
       <c r="AF5" s="173"/>
       <c r="AG5" s="173" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AH5" s="173"/>
       <c r="AI5" s="173"/>
@@ -36000,7 +35969,7 @@
     </row>
     <row r="6" spans="1:39" ht="15" customHeight="1">
       <c r="A6" s="185" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B6" s="185"/>
       <c r="C6" s="185"/>
@@ -36043,7 +36012,7 @@
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
       <c r="A7" s="185" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B7" s="185"/>
       <c r="C7" s="185"/>
@@ -36086,13 +36055,13 @@
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
       <c r="A8" s="185" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B8" s="185"/>
       <c r="C8" s="185"/>
       <c r="D8" s="185"/>
       <c r="E8" s="173" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F8" s="173"/>
       <c r="G8" s="173"/>
@@ -36101,7 +36070,7 @@
       <c r="J8" s="173"/>
       <c r="K8" s="173"/>
       <c r="L8" s="173" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M8" s="173"/>
       <c r="N8" s="173"/>
@@ -36110,7 +36079,7 @@
       <c r="Q8" s="173"/>
       <c r="R8" s="173"/>
       <c r="S8" s="173" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T8" s="173"/>
       <c r="U8" s="173"/>
@@ -36119,7 +36088,7 @@
       <c r="X8" s="173"/>
       <c r="Y8" s="173"/>
       <c r="Z8" s="173" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AA8" s="173"/>
       <c r="AB8" s="173"/>
@@ -36128,7 +36097,7 @@
       <c r="AE8" s="173"/>
       <c r="AF8" s="173"/>
       <c r="AG8" s="173" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AH8" s="173"/>
       <c r="AI8" s="173"/>
@@ -36139,7 +36108,7 @@
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
       <c r="A9" s="185" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B9" s="185"/>
       <c r="C9" s="185"/>
@@ -36182,7 +36151,7 @@
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
       <c r="A10" s="185" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B10" s="185"/>
       <c r="C10" s="185"/>
@@ -36225,13 +36194,13 @@
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
       <c r="A11" s="185" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B11" s="185"/>
       <c r="C11" s="185"/>
       <c r="D11" s="185"/>
       <c r="E11" s="173" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F11" s="173"/>
       <c r="G11" s="173"/>
@@ -36240,7 +36209,7 @@
       <c r="J11" s="173"/>
       <c r="K11" s="173"/>
       <c r="L11" s="173" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M11" s="173"/>
       <c r="N11" s="173"/>
@@ -36249,7 +36218,7 @@
       <c r="Q11" s="173"/>
       <c r="R11" s="173"/>
       <c r="S11" s="173" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="T11" s="173"/>
       <c r="U11" s="173"/>
@@ -36258,7 +36227,7 @@
       <c r="X11" s="173"/>
       <c r="Y11" s="173"/>
       <c r="Z11" s="173" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AA11" s="173"/>
       <c r="AB11" s="173"/>
@@ -36267,7 +36236,7 @@
       <c r="AE11" s="173"/>
       <c r="AF11" s="173"/>
       <c r="AG11" s="173" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH11" s="173"/>
       <c r="AI11" s="173"/>
@@ -36278,7 +36247,7 @@
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
       <c r="A12" s="185" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B12" s="185"/>
       <c r="C12" s="185"/>
@@ -36321,7 +36290,7 @@
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1">
       <c r="A13" s="185" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B13" s="185"/>
       <c r="C13" s="185"/>
@@ -36364,7 +36333,7 @@
     </row>
     <row r="14" spans="1:39">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="67"/>
       <c r="C14" s="6"/>
@@ -36448,7 +36417,7 @@
     </row>
     <row r="16" spans="1:39">
       <c r="A16" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -36570,13 +36539,13 @@
     </row>
     <row r="19" spans="1:39">
       <c r="A19" s="181" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="181"/>
       <c r="C19" s="181"/>
       <c r="D19" s="181"/>
       <c r="E19" s="170" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F19" s="170"/>
       <c r="G19" s="170"/>
@@ -36585,7 +36554,7 @@
       <c r="J19" s="170"/>
       <c r="K19" s="170"/>
       <c r="L19" s="170" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M19" s="170"/>
       <c r="N19" s="170"/>
@@ -36594,7 +36563,7 @@
       <c r="Q19" s="170"/>
       <c r="R19" s="170"/>
       <c r="S19" s="170" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="T19" s="170"/>
       <c r="U19" s="170"/>
@@ -36603,7 +36572,7 @@
       <c r="X19" s="170"/>
       <c r="Y19" s="170"/>
       <c r="Z19" s="170" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AA19" s="170"/>
       <c r="AB19" s="170"/>
@@ -36612,7 +36581,7 @@
       <c r="AE19" s="170"/>
       <c r="AF19" s="170"/>
       <c r="AG19" s="170" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AH19" s="170"/>
       <c r="AI19" s="170"/>
@@ -36627,56 +36596,56 @@
       <c r="C20" s="181"/>
       <c r="D20" s="181"/>
       <c r="E20" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" s="170"/>
       <c r="G20" s="170"/>
       <c r="H20" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I20" s="170"/>
       <c r="J20" s="170"/>
       <c r="K20" s="170"/>
       <c r="L20" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M20" s="170"/>
       <c r="N20" s="170"/>
       <c r="O20" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P20" s="170"/>
       <c r="Q20" s="170"/>
       <c r="R20" s="170"/>
       <c r="S20" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T20" s="170"/>
       <c r="U20" s="170"/>
       <c r="V20" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W20" s="170"/>
       <c r="X20" s="170"/>
       <c r="Y20" s="170"/>
       <c r="Z20" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AA20" s="170"/>
       <c r="AB20" s="170"/>
       <c r="AC20" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AD20" s="170"/>
       <c r="AE20" s="170"/>
       <c r="AF20" s="170"/>
       <c r="AG20" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AH20" s="170"/>
       <c r="AI20" s="170"/>
       <c r="AJ20" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AK20" s="170"/>
       <c r="AL20" s="170"/>
@@ -36684,7 +36653,7 @@
     </row>
     <row r="21" spans="1:39">
       <c r="A21" s="185" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B21" s="185"/>
       <c r="C21" s="185"/>
@@ -36727,7 +36696,7 @@
     </row>
     <row r="22" spans="1:39">
       <c r="A22" s="185" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B22" s="185"/>
       <c r="C22" s="185"/>
@@ -36770,13 +36739,13 @@
     </row>
     <row r="23" spans="1:39">
       <c r="A23" s="181" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" s="181"/>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
       <c r="E23" s="170" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F23" s="170"/>
       <c r="G23" s="170"/>
@@ -36785,7 +36754,7 @@
       <c r="J23" s="170"/>
       <c r="K23" s="170"/>
       <c r="L23" s="170" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M23" s="170"/>
       <c r="N23" s="170"/>
@@ -36794,7 +36763,7 @@
       <c r="Q23" s="170"/>
       <c r="R23" s="170"/>
       <c r="S23" s="170" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T23" s="170"/>
       <c r="U23" s="170"/>
@@ -36803,7 +36772,7 @@
       <c r="X23" s="170"/>
       <c r="Y23" s="170"/>
       <c r="Z23" s="170" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AA23" s="170"/>
       <c r="AB23" s="170"/>
@@ -36812,7 +36781,7 @@
       <c r="AE23" s="170"/>
       <c r="AF23" s="170"/>
       <c r="AG23" s="170" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AH23" s="170"/>
       <c r="AI23" s="170"/>
@@ -36827,56 +36796,56 @@
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
       <c r="E24" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F24" s="170"/>
       <c r="G24" s="170"/>
       <c r="H24" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I24" s="170"/>
       <c r="J24" s="170"/>
       <c r="K24" s="170"/>
       <c r="L24" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M24" s="170"/>
       <c r="N24" s="170"/>
       <c r="O24" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P24" s="170"/>
       <c r="Q24" s="170"/>
       <c r="R24" s="170"/>
       <c r="S24" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T24" s="170"/>
       <c r="U24" s="170"/>
       <c r="V24" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W24" s="170"/>
       <c r="X24" s="170"/>
       <c r="Y24" s="170"/>
       <c r="Z24" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AA24" s="170"/>
       <c r="AB24" s="170"/>
       <c r="AC24" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AD24" s="170"/>
       <c r="AE24" s="170"/>
       <c r="AF24" s="170"/>
       <c r="AG24" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AH24" s="170"/>
       <c r="AI24" s="170"/>
       <c r="AJ24" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AK24" s="170"/>
       <c r="AL24" s="170"/>
@@ -36884,7 +36853,7 @@
     </row>
     <row r="25" spans="1:39">
       <c r="A25" s="185" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" s="185"/>
       <c r="C25" s="185"/>
@@ -36927,7 +36896,7 @@
     </row>
     <row r="26" spans="1:39">
       <c r="A26" s="185" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B26" s="185"/>
       <c r="C26" s="185"/>
@@ -36970,13 +36939,13 @@
     </row>
     <row r="27" spans="1:39">
       <c r="A27" s="181" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" s="181"/>
       <c r="C27" s="181"/>
       <c r="D27" s="181"/>
       <c r="E27" s="170" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F27" s="170"/>
       <c r="G27" s="170"/>
@@ -36985,7 +36954,7 @@
       <c r="J27" s="170"/>
       <c r="K27" s="170"/>
       <c r="L27" s="170" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M27" s="170"/>
       <c r="N27" s="170"/>
@@ -36994,7 +36963,7 @@
       <c r="Q27" s="170"/>
       <c r="R27" s="170"/>
       <c r="S27" s="170" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T27" s="170"/>
       <c r="U27" s="170"/>
@@ -37003,7 +36972,7 @@
       <c r="X27" s="170"/>
       <c r="Y27" s="170"/>
       <c r="Z27" s="170" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AA27" s="170"/>
       <c r="AB27" s="170"/>
@@ -37012,7 +36981,7 @@
       <c r="AE27" s="170"/>
       <c r="AF27" s="170"/>
       <c r="AG27" s="170" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AH27" s="170"/>
       <c r="AI27" s="170"/>
@@ -37027,56 +36996,56 @@
       <c r="C28" s="181"/>
       <c r="D28" s="181"/>
       <c r="E28" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" s="170"/>
       <c r="G28" s="170"/>
       <c r="H28" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I28" s="170"/>
       <c r="J28" s="170"/>
       <c r="K28" s="170"/>
       <c r="L28" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M28" s="170"/>
       <c r="N28" s="170"/>
       <c r="O28" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P28" s="170"/>
       <c r="Q28" s="170"/>
       <c r="R28" s="170"/>
       <c r="S28" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T28" s="170"/>
       <c r="U28" s="170"/>
       <c r="V28" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W28" s="170"/>
       <c r="X28" s="170"/>
       <c r="Y28" s="170"/>
       <c r="Z28" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AA28" s="170"/>
       <c r="AB28" s="170"/>
       <c r="AC28" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AD28" s="170"/>
       <c r="AE28" s="170"/>
       <c r="AF28" s="170"/>
       <c r="AG28" s="170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AH28" s="170"/>
       <c r="AI28" s="170"/>
       <c r="AJ28" s="170" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AK28" s="170"/>
       <c r="AL28" s="170"/>
@@ -37084,7 +37053,7 @@
     </row>
     <row r="29" spans="1:39">
       <c r="A29" s="185" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B29" s="185"/>
       <c r="C29" s="185"/>
@@ -37127,7 +37096,7 @@
     </row>
     <row r="30" spans="1:39">
       <c r="A30" s="185" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B30" s="185"/>
       <c r="C30" s="185"/>
@@ -37170,7 +37139,7 @@
     </row>
     <row r="31" spans="1:39">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" s="68"/>
       <c r="C31" s="68"/>
@@ -37253,32 +37222,32 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -37529,7 +37498,7 @@
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
       <c r="A2" s="108" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -37569,7 +37538,7 @@
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
       <c r="A3" s="71" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -37621,7 +37590,7 @@
       <c r="H5" s="191"/>
       <c r="I5" s="192"/>
       <c r="J5" s="188" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K5" s="188"/>
       <c r="L5" s="188"/>
@@ -37633,7 +37602,7 @@
       <c r="R5" s="188"/>
       <c r="S5" s="188"/>
       <c r="T5" s="188" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="U5" s="188"/>
       <c r="V5" s="188"/>
@@ -37645,7 +37614,7 @@
       <c r="AB5" s="188"/>
       <c r="AC5" s="188"/>
       <c r="AD5" s="188" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AE5" s="188"/>
       <c r="AF5" s="188"/>
@@ -37668,7 +37637,7 @@
       <c r="H6" s="163"/>
       <c r="I6" s="194"/>
       <c r="J6" s="188" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K6" s="188"/>
       <c r="L6" s="188"/>
@@ -37680,7 +37649,7 @@
       <c r="R6" s="188"/>
       <c r="S6" s="188"/>
       <c r="T6" s="188" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U6" s="188"/>
       <c r="V6" s="188"/>
@@ -37692,7 +37661,7 @@
       <c r="AB6" s="188"/>
       <c r="AC6" s="188"/>
       <c r="AD6" s="188" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AE6" s="188"/>
       <c r="AF6" s="188"/>
@@ -37706,7 +37675,7 @@
     </row>
     <row r="7" spans="1:39">
       <c r="A7" s="189" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B7" s="189"/>
       <c r="C7" s="189"/>
@@ -37749,7 +37718,7 @@
     </row>
     <row r="8" spans="1:39">
       <c r="A8" s="189" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B8" s="189"/>
       <c r="C8" s="189"/>
@@ -37792,7 +37761,7 @@
     </row>
     <row r="9" spans="1:39">
       <c r="A9" s="189" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B9" s="189"/>
       <c r="C9" s="189"/>
@@ -37835,17 +37804,17 @@
     </row>
     <row r="11" spans="1:39">
       <c r="A11" s="20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:39">
       <c r="A13" s="20" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:39">
       <c r="A14" s="195" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B14" s="195"/>
       <c r="C14" s="195"/>
@@ -37888,7 +37857,7 @@
     </row>
     <row r="15" spans="1:39">
       <c r="A15" s="196" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B15" s="196"/>
       <c r="C15" s="196"/>
@@ -37931,7 +37900,7 @@
     </row>
     <row r="16" spans="1:39">
       <c r="A16" s="188" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B16" s="188"/>
       <c r="C16" s="188"/>
@@ -37974,7 +37943,7 @@
     </row>
     <row r="17" spans="1:39">
       <c r="A17" s="188" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B17" s="188"/>
       <c r="C17" s="188"/>
@@ -37985,59 +37954,59 @@
       <c r="H17" s="188"/>
       <c r="I17" s="188"/>
       <c r="J17" s="188" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K17" s="188"/>
       <c r="L17" s="188"/>
       <c r="M17" s="188" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N17" s="188"/>
       <c r="O17" s="188"/>
       <c r="P17" s="188" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q17" s="188"/>
       <c r="R17" s="188"/>
       <c r="S17" s="188" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="T17" s="188"/>
       <c r="U17" s="188"/>
       <c r="V17" s="188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W17" s="188"/>
       <c r="X17" s="188"/>
       <c r="Y17" s="188" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="Z17" s="188"/>
       <c r="AA17" s="188"/>
       <c r="AB17" s="188" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AC17" s="188"/>
       <c r="AD17" s="188"/>
       <c r="AE17" s="188" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AF17" s="188"/>
       <c r="AG17" s="188"/>
       <c r="AH17" s="188" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AI17" s="188"/>
       <c r="AJ17" s="188"/>
       <c r="AK17" s="188" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL17" s="188"/>
       <c r="AM17" s="188"/>
     </row>
     <row r="18" spans="1:39">
       <c r="A18" s="188" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B18" s="188"/>
       <c r="C18" s="188"/>
@@ -38080,7 +38049,7 @@
     </row>
     <row r="19" spans="1:39">
       <c r="A19" s="188" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B19" s="188"/>
       <c r="C19" s="188"/>
@@ -38123,7 +38092,7 @@
     </row>
     <row r="20" spans="1:39">
       <c r="A20" s="188" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B20" s="188"/>
       <c r="C20" s="188"/>
@@ -38134,59 +38103,59 @@
       <c r="H20" s="188"/>
       <c r="I20" s="188"/>
       <c r="J20" s="188" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K20" s="188"/>
       <c r="L20" s="188"/>
       <c r="M20" s="188" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N20" s="188"/>
       <c r="O20" s="188"/>
       <c r="P20" s="188" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q20" s="188"/>
       <c r="R20" s="188"/>
       <c r="S20" s="188" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="T20" s="188"/>
       <c r="U20" s="188"/>
       <c r="V20" s="188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W20" s="188"/>
       <c r="X20" s="188"/>
       <c r="Y20" s="188" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="Z20" s="188"/>
       <c r="AA20" s="188"/>
       <c r="AB20" s="188" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AC20" s="188"/>
       <c r="AD20" s="188"/>
       <c r="AE20" s="188" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AF20" s="188"/>
       <c r="AG20" s="188"/>
       <c r="AH20" s="188" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AI20" s="188"/>
       <c r="AJ20" s="188"/>
       <c r="AK20" s="188" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL20" s="188"/>
       <c r="AM20" s="188"/>
     </row>
     <row r="21" spans="1:39">
       <c r="A21" s="188" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -38229,7 +38198,7 @@
     </row>
     <row r="22" spans="1:39">
       <c r="A22" s="188" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -38272,7 +38241,7 @@
     </row>
     <row r="23" spans="1:39">
       <c r="A23" s="196" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B23" s="196"/>
       <c r="C23" s="196"/>
@@ -38315,7 +38284,7 @@
     </row>
     <row r="24" spans="1:39">
       <c r="A24" s="196" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B24" s="196"/>
       <c r="C24" s="196"/>
@@ -38358,7 +38327,7 @@
     </row>
     <row r="25" spans="1:39">
       <c r="A25" s="196" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B25" s="196"/>
       <c r="C25" s="196"/>
@@ -38401,7 +38370,7 @@
     </row>
     <row r="26" spans="1:39">
       <c r="A26" s="196" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B26" s="196"/>
       <c r="C26" s="196"/>
@@ -38444,7 +38413,7 @@
     </row>
     <row r="28" spans="1:39">
       <c r="A28" s="195" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B28" s="195"/>
       <c r="C28" s="195"/>
@@ -38487,7 +38456,7 @@
     </row>
     <row r="29" spans="1:39">
       <c r="A29" s="196" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B29" s="196"/>
       <c r="C29" s="196"/>
@@ -38530,7 +38499,7 @@
     </row>
     <row r="30" spans="1:39">
       <c r="A30" s="188" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B30" s="188"/>
       <c r="C30" s="188"/>
@@ -38573,7 +38542,7 @@
     </row>
     <row r="31" spans="1:39">
       <c r="A31" s="188" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B31" s="188"/>
       <c r="C31" s="188"/>
@@ -38584,7 +38553,7 @@
       <c r="H31" s="188"/>
       <c r="I31" s="188"/>
       <c r="J31" s="188" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K31" s="188"/>
       <c r="L31" s="188"/>
@@ -38592,7 +38561,7 @@
       <c r="N31" s="188"/>
       <c r="O31" s="188"/>
       <c r="P31" s="188" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q31" s="188"/>
       <c r="R31" s="188"/>
@@ -38600,7 +38569,7 @@
       <c r="T31" s="188"/>
       <c r="U31" s="188"/>
       <c r="V31" s="188" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="W31" s="188"/>
       <c r="X31" s="188"/>
@@ -38608,7 +38577,7 @@
       <c r="Z31" s="188"/>
       <c r="AA31" s="188"/>
       <c r="AB31" s="188" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AC31" s="188"/>
       <c r="AD31" s="188"/>
@@ -38616,7 +38585,7 @@
       <c r="AF31" s="188"/>
       <c r="AG31" s="188"/>
       <c r="AH31" s="188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AI31" s="188"/>
       <c r="AJ31" s="188"/>
@@ -38708,7 +38677,7 @@
     </row>
     <row r="34" spans="1:39">
       <c r="A34" s="188" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B34" s="188"/>
       <c r="C34" s="188"/>
@@ -38719,7 +38688,7 @@
       <c r="H34" s="188"/>
       <c r="I34" s="188"/>
       <c r="J34" s="188" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K34" s="188"/>
       <c r="L34" s="188"/>
@@ -38727,7 +38696,7 @@
       <c r="N34" s="188"/>
       <c r="O34" s="188"/>
       <c r="P34" s="188" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q34" s="188"/>
       <c r="R34" s="188"/>
@@ -38735,7 +38704,7 @@
       <c r="T34" s="188"/>
       <c r="U34" s="188"/>
       <c r="V34" s="188" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="W34" s="188"/>
       <c r="X34" s="188"/>
@@ -38743,7 +38712,7 @@
       <c r="Z34" s="188"/>
       <c r="AA34" s="188"/>
       <c r="AB34" s="188" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AC34" s="188"/>
       <c r="AD34" s="188"/>
@@ -38751,7 +38720,7 @@
       <c r="AF34" s="188"/>
       <c r="AG34" s="188"/>
       <c r="AH34" s="188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AI34" s="188"/>
       <c r="AJ34" s="188"/>
@@ -38843,7 +38812,7 @@
     </row>
     <row r="37" spans="1:39">
       <c r="A37" s="188" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B37" s="188"/>
       <c r="C37" s="188"/>
@@ -38854,7 +38823,7 @@
       <c r="H37" s="188"/>
       <c r="I37" s="188"/>
       <c r="J37" s="188" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K37" s="188"/>
       <c r="L37" s="188"/>
@@ -38862,7 +38831,7 @@
       <c r="N37" s="188"/>
       <c r="O37" s="188"/>
       <c r="P37" s="188" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q37" s="188"/>
       <c r="R37" s="188"/>
@@ -38870,7 +38839,7 @@
       <c r="T37" s="188"/>
       <c r="U37" s="188"/>
       <c r="V37" s="188" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="W37" s="188"/>
       <c r="X37" s="188"/>
@@ -38878,7 +38847,7 @@
       <c r="Z37" s="188"/>
       <c r="AA37" s="188"/>
       <c r="AB37" s="188" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AC37" s="188"/>
       <c r="AD37" s="188"/>
@@ -38886,7 +38855,7 @@
       <c r="AF37" s="188"/>
       <c r="AG37" s="188"/>
       <c r="AH37" s="188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AI37" s="188"/>
       <c r="AJ37" s="188"/>
@@ -38978,7 +38947,7 @@
     </row>
     <row r="40" spans="1:39">
       <c r="A40" s="188" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B40" s="188"/>
       <c r="C40" s="188"/>
@@ -38989,7 +38958,7 @@
       <c r="H40" s="188"/>
       <c r="I40" s="188"/>
       <c r="J40" s="188" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K40" s="188"/>
       <c r="L40" s="188"/>
@@ -38997,7 +38966,7 @@
       <c r="N40" s="188"/>
       <c r="O40" s="188"/>
       <c r="P40" s="188" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q40" s="188"/>
       <c r="R40" s="188"/>
@@ -39005,7 +38974,7 @@
       <c r="T40" s="188"/>
       <c r="U40" s="188"/>
       <c r="V40" s="188" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="W40" s="188"/>
       <c r="X40" s="188"/>
@@ -39013,7 +38982,7 @@
       <c r="Z40" s="188"/>
       <c r="AA40" s="188"/>
       <c r="AB40" s="188" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AC40" s="188"/>
       <c r="AD40" s="188"/>
@@ -39021,7 +38990,7 @@
       <c r="AF40" s="188"/>
       <c r="AG40" s="188"/>
       <c r="AH40" s="188" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AI40" s="188"/>
       <c r="AJ40" s="188"/>
@@ -39113,7 +39082,7 @@
     </row>
     <row r="43" spans="1:39">
       <c r="A43" s="195" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B43" s="195"/>
       <c r="C43" s="195"/>
@@ -39156,7 +39125,7 @@
     </row>
     <row r="44" spans="1:39">
       <c r="A44" s="195" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B44" s="195"/>
       <c r="C44" s="195"/>
@@ -39199,7 +39168,7 @@
     </row>
     <row r="45" spans="1:39" ht="14.4">
       <c r="A45" s="197" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B45" s="197"/>
       <c r="C45" s="197"/>
@@ -39242,7 +39211,7 @@
     </row>
     <row r="46" spans="1:39">
       <c r="A46" s="198" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B46" s="199"/>
       <c r="C46" s="199"/>
@@ -39599,7 +39568,7 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="110" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B2" s="111"/>
       <c r="C2" s="111"/>
@@ -39627,7 +39596,7 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="20" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -39635,7 +39604,7 @@
     </row>
     <row r="5" spans="1:28" ht="21">
       <c r="A5" s="112" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -39643,12 +39612,12 @@
     </row>
     <row r="7" spans="1:28" ht="21">
       <c r="A7" s="112" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="21">
       <c r="A9" s="112" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -39656,7 +39625,7 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="28" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -39664,7 +39633,7 @@
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="110" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="Q13" s="130"/>
       <c r="R13" s="130"/>
@@ -39677,7 +39646,7 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -39685,7 +39654,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -39693,7 +39662,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -39701,7 +39670,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -39712,32 +39681,32 @@
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="113" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="113" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="113" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="113" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="113" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -39748,7 +39717,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -39811,7 +39780,7 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="54" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B2" s="114"/>
       <c r="C2" s="114"/>
@@ -39826,7 +39795,7 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="20" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" spans="1:28">
@@ -39834,7 +39803,7 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -39842,7 +39811,7 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -39850,17 +39819,17 @@
     </row>
     <row r="10" spans="1:28">
       <c r="A10" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N10" s="21"/>
       <c r="O10" s="130"/>
       <c r="P10" s="130"/>
       <c r="Q10" s="130"/>
       <c r="R10" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="S10" s="21"/>
       <c r="T10" s="21"/>
@@ -39870,7 +39839,7 @@
     </row>
     <row r="11" spans="1:28" ht="14.4">
       <c r="A11" s="201" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B11" s="202"/>
       <c r="C11" s="202"/>
@@ -39882,7 +39851,7 @@
       <c r="I11" s="203"/>
       <c r="J11" s="204"/>
       <c r="K11" s="205" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L11" s="200"/>
       <c r="M11" s="200"/>
@@ -39890,7 +39859,7 @@
       <c r="O11" s="200"/>
       <c r="P11" s="200"/>
       <c r="Q11" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="R11" s="200"/>
       <c r="S11" s="200"/>
@@ -39898,7 +39867,7 @@
       <c r="U11" s="200"/>
       <c r="V11" s="200"/>
       <c r="W11" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="X11" s="200"/>
       <c r="Y11" s="200"/>
@@ -39908,7 +39877,7 @@
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="195" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B12" s="195"/>
       <c r="C12" s="195"/>
@@ -39940,7 +39909,7 @@
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="195" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B13" s="195"/>
       <c r="C13" s="195"/>
@@ -39972,7 +39941,7 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="195" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B14" s="195"/>
       <c r="C14" s="195"/>
@@ -40004,7 +39973,7 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="195" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B15" s="195"/>
       <c r="C15" s="195"/>
@@ -40036,7 +40005,7 @@
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="195" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B16" s="195"/>
       <c r="C16" s="195"/>
@@ -40068,17 +40037,17 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M18" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N18" s="21"/>
       <c r="O18" s="130"/>
       <c r="P18" s="130"/>
       <c r="Q18" s="130"/>
       <c r="R18" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="S18" s="21"/>
       <c r="T18" s="21"/>
@@ -40088,7 +40057,7 @@
     </row>
     <row r="19" spans="1:28" ht="14.4">
       <c r="A19" s="201" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B19" s="202"/>
       <c r="C19" s="202"/>
@@ -40100,7 +40069,7 @@
       <c r="I19" s="203"/>
       <c r="J19" s="204"/>
       <c r="K19" s="205" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L19" s="200"/>
       <c r="M19" s="200"/>
@@ -40108,7 +40077,7 @@
       <c r="O19" s="200"/>
       <c r="P19" s="200"/>
       <c r="Q19" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="R19" s="200"/>
       <c r="S19" s="200"/>
@@ -40116,7 +40085,7 @@
       <c r="U19" s="200"/>
       <c r="V19" s="200"/>
       <c r="W19" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="X19" s="200"/>
       <c r="Y19" s="200"/>
@@ -40126,7 +40095,7 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="195" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B20" s="195"/>
       <c r="C20" s="195"/>
@@ -40158,7 +40127,7 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="195" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B21" s="195"/>
       <c r="C21" s="195"/>
@@ -40190,7 +40159,7 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="195" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B22" s="195"/>
       <c r="C22" s="195"/>
@@ -40222,7 +40191,7 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="195" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B23" s="195"/>
       <c r="C23" s="195"/>
@@ -40254,7 +40223,7 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="195" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B24" s="195"/>
       <c r="C24" s="195"/>
@@ -40286,17 +40255,17 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M26" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N26" s="21"/>
       <c r="O26" s="130"/>
       <c r="P26" s="130"/>
       <c r="Q26" s="130"/>
       <c r="R26" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="S26" s="21"/>
       <c r="T26" s="21"/>
@@ -40306,7 +40275,7 @@
     </row>
     <row r="27" spans="1:28" ht="14.4">
       <c r="A27" s="201" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B27" s="202"/>
       <c r="C27" s="202"/>
@@ -40318,7 +40287,7 @@
       <c r="I27" s="203"/>
       <c r="J27" s="204"/>
       <c r="K27" s="205" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L27" s="200"/>
       <c r="M27" s="200"/>
@@ -40326,7 +40295,7 @@
       <c r="O27" s="200"/>
       <c r="P27" s="200"/>
       <c r="Q27" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="R27" s="200"/>
       <c r="S27" s="200"/>
@@ -40334,7 +40303,7 @@
       <c r="U27" s="200"/>
       <c r="V27" s="200"/>
       <c r="W27" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="X27" s="200"/>
       <c r="Y27" s="200"/>
@@ -40344,7 +40313,7 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="195" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B28" s="195"/>
       <c r="C28" s="195"/>
@@ -40376,7 +40345,7 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="195" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B29" s="195"/>
       <c r="C29" s="195"/>
@@ -40408,7 +40377,7 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="195" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B30" s="195"/>
       <c r="C30" s="195"/>
@@ -40440,7 +40409,7 @@
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="195" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B31" s="195"/>
       <c r="C31" s="195"/>
@@ -40472,7 +40441,7 @@
     </row>
     <row r="32" spans="1:28">
       <c r="A32" s="195" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B32" s="195"/>
       <c r="C32" s="195"/>
@@ -40504,17 +40473,17 @@
     </row>
     <row r="34" spans="1:28">
       <c r="A34" s="21" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M34" s="21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N34" s="21"/>
       <c r="O34" s="130"/>
       <c r="P34" s="130"/>
       <c r="Q34" s="130"/>
       <c r="R34" s="21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="S34" s="21"/>
       <c r="T34" s="21"/>
@@ -40524,7 +40493,7 @@
     </row>
     <row r="35" spans="1:28" ht="14.4">
       <c r="A35" s="201" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B35" s="202"/>
       <c r="C35" s="202"/>
@@ -40536,7 +40505,7 @@
       <c r="I35" s="203"/>
       <c r="J35" s="204"/>
       <c r="K35" s="205" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L35" s="200"/>
       <c r="M35" s="200"/>
@@ -40544,7 +40513,7 @@
       <c r="O35" s="200"/>
       <c r="P35" s="200"/>
       <c r="Q35" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="R35" s="200"/>
       <c r="S35" s="200"/>
@@ -40552,7 +40521,7 @@
       <c r="U35" s="200"/>
       <c r="V35" s="200"/>
       <c r="W35" s="200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="X35" s="200"/>
       <c r="Y35" s="200"/>
@@ -40562,7 +40531,7 @@
     </row>
     <row r="36" spans="1:28">
       <c r="A36" s="195" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B36" s="195"/>
       <c r="C36" s="195"/>
@@ -40594,7 +40563,7 @@
     </row>
     <row r="37" spans="1:28">
       <c r="A37" s="195" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B37" s="195"/>
       <c r="C37" s="195"/>
@@ -40626,7 +40595,7 @@
     </row>
     <row r="38" spans="1:28">
       <c r="A38" s="195" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B38" s="195"/>
       <c r="C38" s="195"/>
@@ -40658,7 +40627,7 @@
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="195" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B39" s="195"/>
       <c r="C39" s="195"/>
@@ -40690,7 +40659,7 @@
     </row>
     <row r="40" spans="1:28">
       <c r="A40" s="195" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -40722,52 +40691,52 @@
     </row>
     <row r="41" spans="1:28">
       <c r="A41" s="20" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:28">
       <c r="A42" s="113" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="43" spans="1:28">
       <c r="A43" s="113" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="44" spans="1:28">
       <c r="A44" s="113" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="45" spans="1:28">
       <c r="A45" s="113" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" spans="1:28">
       <c r="A46" s="113" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="47" spans="1:28">
       <c r="A47" s="113" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="48" spans="1:28">
       <c r="A48" s="20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="20" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="51" spans="1:1">
